--- a/mom/docs/forms/frm-600-inspection/FRM-655_Rework_Repair_Order_and_Verification_Record.xlsx
+++ b/mom/docs/forms/frm-600-inspection/FRM-655_Rework_Repair_Order_and_Verification_Record.xlsx
@@ -791,7 +791,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="265">
+  <borders count="261">
     <border>
       <left/>
       <right/>
@@ -3610,88 +3610,37 @@
       <left style="thin">
         <color rgb="000078D4"/>
       </left>
-      <right style="thin">
+      <right/>
+      <bottom style="thin">
         <color rgb="000078D4"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00E2E8F0"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <bottom style="thin">
         <color rgb="000078D4"/>
-      </left>
-      <right/>
-      <bottom style="thin">
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
         <color rgb="000078D4"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
+      </right>
       <bottom style="thin">
         <color rgb="000078D4"/>
       </bottom>
     </border>
     <border>
-      <left/>
-      <right style="thin">
+      <left style="thin">
         <color rgb="000078D4"/>
-      </right>
-      <bottom style="thin">
+      </left>
+      <right style="thin">
         <color rgb="000078D4"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
+      </right>
+      <bottom style="thin">
         <color rgb="000078D4"/>
-      </left>
-      <right style="thin">
-        <color rgb="000078D4"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="000078D4"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00E2E8F0"/>
-      </right>
-      <top style="thin">
-        <color rgb="000078D4"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000078D4"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="000078D4"/>
-      </left>
-      <right style="thin">
-        <color rgb="00E2E8F0"/>
-      </right>
-      <top style="thin">
-        <color rgb="000078D4"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000078D4"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00E2E8F0"/>
-      </right>
-      <top style="thin">
-        <color rgb="000078D4"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000078D4"/>
-      </bottom>
-      <diagonal/>
+      </bottom>
     </border>
     <border>
       <left/>
@@ -3761,7 +3710,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="531">
+  <cellXfs count="524">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -4958,24 +4907,8 @@
     <xf numFmtId="0" fontId="80" fillId="47" borderId="249" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="253" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="47" borderId="249" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="49" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="47" borderId="254" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="49" borderId="256" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="257" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="80" fillId="47" borderId="255" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="49" borderId="255" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="47" borderId="212" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="81" fillId="50" borderId="222" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4985,41 +4918,46 @@
     <xf numFmtId="0" fontId="81" fillId="50" borderId="221" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="79" fillId="49" borderId="259" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="79" fillId="49" borderId="255" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="51" borderId="258" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="82" fillId="51" borderId="254" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="47" borderId="258" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="80" fillId="47" borderId="254" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="49" borderId="258" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="83" fillId="49" borderId="254" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="47" borderId="258" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="80" fillId="47" borderId="254" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="80" fillId="47" borderId="248" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="84" fillId="52" borderId="258" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="84" fillId="52" borderId="254" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="53" borderId="258" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="80" fillId="53" borderId="254" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="49" borderId="258" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="53" borderId="258" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="49" borderId="261" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="79" fillId="49" borderId="257" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="49" borderId="260" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="47" borderId="260" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="80" fillId="47" borderId="260" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="82" fillId="51" borderId="256" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="47" borderId="253" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="80" fillId="53" borderId="256" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="49" borderId="256" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="47" borderId="256" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="47" borderId="252" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="79" fillId="49" borderId="213" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -5030,13 +4968,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="214" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="215" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="262" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="258" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="235" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="263" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="259" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="86" fillId="48" borderId="213" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="47" borderId="264" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="260" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5146,6 +5084,46 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>QMS</author>
+  </authors>
+  <commentList>
+    <comment ref="A9" authorId="0" shapeId="0">
+      <text>
+        <t>Số lệnh sửa
+Mã duy nhất của lệnh gia công lại / sửa chữa.</t>
+      </text>
+    </comment>
+    <comment ref="A11" authorId="0" shapeId="0">
+      <text>
+        <t>Số NCR
+FRM-651 — phiếu không phù hợp đã mở cho lô này.</t>
+      </text>
+    </comment>
+    <comment ref="U11" authorId="0" shapeId="0">
+      <text>
+        <t>Số lượng sửa
+Số chi tiết thuộc phạm vi lệnh sửa.</t>
+      </text>
+    </comment>
+    <comment ref="A13" authorId="0" shapeId="0">
+      <text>
+        <t>Người duyệt sửa
+Sửa chỉ được tiến hành sau khi có duyệt.</t>
+      </text>
+    </comment>
+    <comment ref="AF27" authorId="0" shapeId="0">
+      <text>
+        <t>Kết quả
+PASS / HOLD / FAIL — chọn từ danh sách.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5470,7 +5448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:BS50"/>
+  <dimension ref="A2:AN47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.375" customWidth="1" style="264" min="1" max="1"/>
@@ -5716,7 +5694,7 @@
       <c r="AN6" s="272" t="n"/>
     </row>
     <row r="7" ht="4" customHeight="1" s="264">
-      <c r="A7" s="530" t="n"/>
+      <c r="A7" s="523" t="n"/>
       <c r="B7" s="26" t="n"/>
       <c r="C7" s="26" t="n"/>
       <c r="D7" s="26" t="n"/>
@@ -6054,7 +6032,7 @@
       <c r="AN13" s="493" t="n"/>
     </row>
     <row r="14" ht="4" customHeight="1" s="264">
-      <c r="A14" s="530" t="n"/>
+      <c r="A14" s="523" t="n"/>
       <c r="B14" s="26" t="n"/>
       <c r="C14" s="26" t="n"/>
       <c r="D14" s="26" t="n"/>
@@ -6098,7 +6076,7 @@
     <row r="15" ht="17" customHeight="1" s="264">
       <c r="A15" s="470" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.  DEFECT DESCRIPTION &amp; APPROVED REWORK METHOD</t>
+          <t xml:space="preserve">  2.  DEFECT DESCRIPTION</t>
         </is>
       </c>
       <c r="B15" s="471" t="n"/>
@@ -6144,7 +6122,7 @@
     <row r="16" ht="17" customHeight="1" s="264">
       <c r="A16" s="494" t="inlineStr">
         <is>
-          <t>DEFECT DESCRIPTION</t>
+          <t>Describe the defect: what, where, extent. Attach photo reference.</t>
         </is>
       </c>
       <c r="B16" s="474" t="n"/>
@@ -6231,178 +6209,182 @@
     </row>
     <row r="18" ht="20" customHeight="1" s="264">
       <c r="A18" s="496" t="n"/>
-      <c r="B18" s="481" t="n"/>
-      <c r="C18" s="481" t="n"/>
-      <c r="D18" s="481" t="n"/>
-      <c r="E18" s="481" t="n"/>
-      <c r="F18" s="481" t="n"/>
-      <c r="G18" s="481" t="n"/>
-      <c r="H18" s="481" t="n"/>
-      <c r="I18" s="481" t="n"/>
-      <c r="J18" s="481" t="n"/>
-      <c r="K18" s="481" t="n"/>
-      <c r="L18" s="481" t="n"/>
-      <c r="M18" s="481" t="n"/>
-      <c r="N18" s="481" t="n"/>
-      <c r="O18" s="481" t="n"/>
-      <c r="P18" s="481" t="n"/>
-      <c r="Q18" s="481" t="n"/>
-      <c r="R18" s="481" t="n"/>
-      <c r="S18" s="481" t="n"/>
-      <c r="T18" s="481" t="n"/>
-      <c r="U18" s="481" t="n"/>
-      <c r="V18" s="481" t="n"/>
-      <c r="W18" s="481" t="n"/>
-      <c r="X18" s="481" t="n"/>
-      <c r="Y18" s="481" t="n"/>
-      <c r="Z18" s="481" t="n"/>
-      <c r="AA18" s="481" t="n"/>
-      <c r="AB18" s="481" t="n"/>
-      <c r="AC18" s="481" t="n"/>
-      <c r="AD18" s="481" t="n"/>
-      <c r="AE18" s="481" t="n"/>
-      <c r="AF18" s="481" t="n"/>
-      <c r="AG18" s="481" t="n"/>
-      <c r="AH18" s="481" t="n"/>
-      <c r="AI18" s="481" t="n"/>
-      <c r="AJ18" s="481" t="n"/>
-      <c r="AK18" s="481" t="n"/>
-      <c r="AL18" s="481" t="n"/>
-      <c r="AM18" s="481" t="n"/>
-      <c r="AN18" s="486" t="n"/>
+      <c r="B18" s="488" t="n"/>
+      <c r="C18" s="488" t="n"/>
+      <c r="D18" s="488" t="n"/>
+      <c r="E18" s="488" t="n"/>
+      <c r="F18" s="488" t="n"/>
+      <c r="G18" s="488" t="n"/>
+      <c r="H18" s="488" t="n"/>
+      <c r="I18" s="488" t="n"/>
+      <c r="J18" s="488" t="n"/>
+      <c r="K18" s="488" t="n"/>
+      <c r="L18" s="488" t="n"/>
+      <c r="M18" s="488" t="n"/>
+      <c r="N18" s="488" t="n"/>
+      <c r="O18" s="488" t="n"/>
+      <c r="P18" s="488" t="n"/>
+      <c r="Q18" s="488" t="n"/>
+      <c r="R18" s="488" t="n"/>
+      <c r="S18" s="488" t="n"/>
+      <c r="T18" s="488" t="n"/>
+      <c r="U18" s="488" t="n"/>
+      <c r="V18" s="488" t="n"/>
+      <c r="W18" s="488" t="n"/>
+      <c r="X18" s="488" t="n"/>
+      <c r="Y18" s="488" t="n"/>
+      <c r="Z18" s="488" t="n"/>
+      <c r="AA18" s="488" t="n"/>
+      <c r="AB18" s="488" t="n"/>
+      <c r="AC18" s="488" t="n"/>
+      <c r="AD18" s="488" t="n"/>
+      <c r="AE18" s="488" t="n"/>
+      <c r="AF18" s="488" t="n"/>
+      <c r="AG18" s="488" t="n"/>
+      <c r="AH18" s="488" t="n"/>
+      <c r="AI18" s="488" t="n"/>
+      <c r="AJ18" s="488" t="n"/>
+      <c r="AK18" s="488" t="n"/>
+      <c r="AL18" s="488" t="n"/>
+      <c r="AM18" s="488" t="n"/>
+      <c r="AN18" s="493" t="n"/>
     </row>
-    <row r="19" ht="20" customHeight="1" s="264">
-      <c r="A19" s="496" t="n"/>
-      <c r="B19" s="481" t="n"/>
-      <c r="C19" s="481" t="n"/>
-      <c r="D19" s="481" t="n"/>
-      <c r="E19" s="481" t="n"/>
-      <c r="F19" s="481" t="n"/>
-      <c r="G19" s="481" t="n"/>
-      <c r="H19" s="481" t="n"/>
-      <c r="I19" s="481" t="n"/>
-      <c r="J19" s="481" t="n"/>
-      <c r="K19" s="481" t="n"/>
-      <c r="L19" s="481" t="n"/>
-      <c r="M19" s="481" t="n"/>
-      <c r="N19" s="481" t="n"/>
-      <c r="O19" s="481" t="n"/>
-      <c r="P19" s="481" t="n"/>
-      <c r="Q19" s="481" t="n"/>
-      <c r="R19" s="481" t="n"/>
-      <c r="S19" s="481" t="n"/>
-      <c r="T19" s="481" t="n"/>
-      <c r="U19" s="481" t="n"/>
-      <c r="V19" s="481" t="n"/>
-      <c r="W19" s="481" t="n"/>
-      <c r="X19" s="481" t="n"/>
-      <c r="Y19" s="481" t="n"/>
-      <c r="Z19" s="481" t="n"/>
-      <c r="AA19" s="481" t="n"/>
-      <c r="AB19" s="481" t="n"/>
-      <c r="AC19" s="481" t="n"/>
-      <c r="AD19" s="481" t="n"/>
-      <c r="AE19" s="481" t="n"/>
-      <c r="AF19" s="481" t="n"/>
-      <c r="AG19" s="481" t="n"/>
-      <c r="AH19" s="481" t="n"/>
-      <c r="AI19" s="481" t="n"/>
-      <c r="AJ19" s="481" t="n"/>
-      <c r="AK19" s="481" t="n"/>
-      <c r="AL19" s="481" t="n"/>
-      <c r="AM19" s="481" t="n"/>
-      <c r="AN19" s="486" t="n"/>
+    <row r="19" ht="4" customHeight="1" s="264">
+      <c r="A19" s="523" t="n"/>
+      <c r="B19" s="26" t="n"/>
+      <c r="C19" s="26" t="n"/>
+      <c r="D19" s="26" t="n"/>
+      <c r="E19" s="26" t="n"/>
+      <c r="F19" s="26" t="n"/>
+      <c r="G19" s="26" t="n"/>
+      <c r="H19" s="26" t="n"/>
+      <c r="I19" s="26" t="n"/>
+      <c r="J19" s="26" t="n"/>
+      <c r="K19" s="26" t="n"/>
+      <c r="L19" s="26" t="n"/>
+      <c r="M19" s="26" t="n"/>
+      <c r="N19" s="26" t="n"/>
+      <c r="O19" s="26" t="n"/>
+      <c r="P19" s="26" t="n"/>
+      <c r="Q19" s="26" t="n"/>
+      <c r="R19" s="26" t="n"/>
+      <c r="S19" s="26" t="n"/>
+      <c r="T19" s="26" t="n"/>
+      <c r="U19" s="26" t="n"/>
+      <c r="V19" s="26" t="n"/>
+      <c r="W19" s="26" t="n"/>
+      <c r="X19" s="26" t="n"/>
+      <c r="Y19" s="26" t="n"/>
+      <c r="Z19" s="26" t="n"/>
+      <c r="AA19" s="26" t="n"/>
+      <c r="AB19" s="26" t="n"/>
+      <c r="AC19" s="26" t="n"/>
+      <c r="AD19" s="26" t="n"/>
+      <c r="AE19" s="26" t="n"/>
+      <c r="AF19" s="26" t="n"/>
+      <c r="AG19" s="26" t="n"/>
+      <c r="AH19" s="26" t="n"/>
+      <c r="AI19" s="26" t="n"/>
+      <c r="AJ19" s="26" t="n"/>
+      <c r="AK19" s="26" t="n"/>
+      <c r="AL19" s="26" t="n"/>
+      <c r="AM19" s="26" t="n"/>
+      <c r="AN19" s="26" t="n"/>
     </row>
     <row r="20" ht="17" customHeight="1" s="264">
-      <c r="A20" s="497" t="inlineStr">
-        <is>
-          <t>APPROVED REWORK / REPAIR METHOD</t>
-        </is>
-      </c>
-      <c r="B20" s="481" t="n"/>
-      <c r="C20" s="481" t="n"/>
-      <c r="D20" s="481" t="n"/>
-      <c r="E20" s="481" t="n"/>
-      <c r="F20" s="481" t="n"/>
-      <c r="G20" s="481" t="n"/>
-      <c r="H20" s="481" t="n"/>
-      <c r="I20" s="481" t="n"/>
-      <c r="J20" s="481" t="n"/>
-      <c r="K20" s="481" t="n"/>
-      <c r="L20" s="481" t="n"/>
-      <c r="M20" s="481" t="n"/>
-      <c r="N20" s="481" t="n"/>
-      <c r="O20" s="481" t="n"/>
-      <c r="P20" s="481" t="n"/>
-      <c r="Q20" s="481" t="n"/>
-      <c r="R20" s="481" t="n"/>
-      <c r="S20" s="481" t="n"/>
-      <c r="T20" s="481" t="n"/>
-      <c r="U20" s="481" t="n"/>
-      <c r="V20" s="481" t="n"/>
-      <c r="W20" s="481" t="n"/>
-      <c r="X20" s="481" t="n"/>
-      <c r="Y20" s="481" t="n"/>
-      <c r="Z20" s="481" t="n"/>
-      <c r="AA20" s="481" t="n"/>
-      <c r="AB20" s="481" t="n"/>
-      <c r="AC20" s="481" t="n"/>
-      <c r="AD20" s="481" t="n"/>
-      <c r="AE20" s="481" t="n"/>
-      <c r="AF20" s="481" t="n"/>
-      <c r="AG20" s="481" t="n"/>
-      <c r="AH20" s="481" t="n"/>
-      <c r="AI20" s="481" t="n"/>
-      <c r="AJ20" s="481" t="n"/>
-      <c r="AK20" s="481" t="n"/>
-      <c r="AL20" s="481" t="n"/>
-      <c r="AM20" s="481" t="n"/>
-      <c r="AN20" s="486" t="n"/>
+      <c r="A20" s="470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3.  APPROVED REWORK / REPAIR METHOD</t>
+        </is>
+      </c>
+      <c r="B20" s="471" t="n"/>
+      <c r="C20" s="471" t="n"/>
+      <c r="D20" s="471" t="n"/>
+      <c r="E20" s="471" t="n"/>
+      <c r="F20" s="471" t="n"/>
+      <c r="G20" s="471" t="n"/>
+      <c r="H20" s="471" t="n"/>
+      <c r="I20" s="471" t="n"/>
+      <c r="J20" s="471" t="n"/>
+      <c r="K20" s="471" t="n"/>
+      <c r="L20" s="471" t="n"/>
+      <c r="M20" s="471" t="n"/>
+      <c r="N20" s="471" t="n"/>
+      <c r="O20" s="471" t="n"/>
+      <c r="P20" s="471" t="n"/>
+      <c r="Q20" s="471" t="n"/>
+      <c r="R20" s="471" t="n"/>
+      <c r="S20" s="471" t="n"/>
+      <c r="T20" s="471" t="n"/>
+      <c r="U20" s="471" t="n"/>
+      <c r="V20" s="471" t="n"/>
+      <c r="W20" s="471" t="n"/>
+      <c r="X20" s="471" t="n"/>
+      <c r="Y20" s="471" t="n"/>
+      <c r="Z20" s="471" t="n"/>
+      <c r="AA20" s="471" t="n"/>
+      <c r="AB20" s="471" t="n"/>
+      <c r="AC20" s="471" t="n"/>
+      <c r="AD20" s="471" t="n"/>
+      <c r="AE20" s="471" t="n"/>
+      <c r="AF20" s="471" t="n"/>
+      <c r="AG20" s="471" t="n"/>
+      <c r="AH20" s="471" t="n"/>
+      <c r="AI20" s="471" t="n"/>
+      <c r="AJ20" s="471" t="n"/>
+      <c r="AK20" s="471" t="n"/>
+      <c r="AL20" s="471" t="n"/>
+      <c r="AM20" s="471" t="n"/>
+      <c r="AN20" s="472" t="n"/>
     </row>
-    <row r="21" ht="20" customHeight="1" s="264">
-      <c r="A21" s="495" t="n"/>
-      <c r="B21" s="481" t="n"/>
-      <c r="C21" s="481" t="n"/>
-      <c r="D21" s="481" t="n"/>
-      <c r="E21" s="481" t="n"/>
-      <c r="F21" s="481" t="n"/>
-      <c r="G21" s="481" t="n"/>
-      <c r="H21" s="481" t="n"/>
-      <c r="I21" s="481" t="n"/>
-      <c r="J21" s="481" t="n"/>
-      <c r="K21" s="481" t="n"/>
-      <c r="L21" s="481" t="n"/>
-      <c r="M21" s="481" t="n"/>
-      <c r="N21" s="481" t="n"/>
-      <c r="O21" s="481" t="n"/>
-      <c r="P21" s="481" t="n"/>
-      <c r="Q21" s="481" t="n"/>
-      <c r="R21" s="481" t="n"/>
-      <c r="S21" s="481" t="n"/>
-      <c r="T21" s="481" t="n"/>
-      <c r="U21" s="481" t="n"/>
-      <c r="V21" s="481" t="n"/>
-      <c r="W21" s="481" t="n"/>
-      <c r="X21" s="481" t="n"/>
-      <c r="Y21" s="481" t="n"/>
-      <c r="Z21" s="481" t="n"/>
-      <c r="AA21" s="481" t="n"/>
-      <c r="AB21" s="481" t="n"/>
-      <c r="AC21" s="481" t="n"/>
-      <c r="AD21" s="481" t="n"/>
-      <c r="AE21" s="481" t="n"/>
-      <c r="AF21" s="481" t="n"/>
-      <c r="AG21" s="481" t="n"/>
-      <c r="AH21" s="481" t="n"/>
-      <c r="AI21" s="481" t="n"/>
-      <c r="AJ21" s="481" t="n"/>
-      <c r="AK21" s="481" t="n"/>
-      <c r="AL21" s="481" t="n"/>
-      <c r="AM21" s="481" t="n"/>
-      <c r="AN21" s="486" t="n"/>
+    <row r="21" ht="17" customHeight="1" s="264">
+      <c r="A21" s="494" t="inlineStr">
+        <is>
+          <t>Approved method, sequence and any special tooling / process. No deviation permitted.</t>
+        </is>
+      </c>
+      <c r="B21" s="474" t="n"/>
+      <c r="C21" s="474" t="n"/>
+      <c r="D21" s="474" t="n"/>
+      <c r="E21" s="474" t="n"/>
+      <c r="F21" s="474" t="n"/>
+      <c r="G21" s="474" t="n"/>
+      <c r="H21" s="474" t="n"/>
+      <c r="I21" s="474" t="n"/>
+      <c r="J21" s="474" t="n"/>
+      <c r="K21" s="474" t="n"/>
+      <c r="L21" s="474" t="n"/>
+      <c r="M21" s="474" t="n"/>
+      <c r="N21" s="474" t="n"/>
+      <c r="O21" s="474" t="n"/>
+      <c r="P21" s="474" t="n"/>
+      <c r="Q21" s="474" t="n"/>
+      <c r="R21" s="474" t="n"/>
+      <c r="S21" s="474" t="n"/>
+      <c r="T21" s="474" t="n"/>
+      <c r="U21" s="474" t="n"/>
+      <c r="V21" s="474" t="n"/>
+      <c r="W21" s="474" t="n"/>
+      <c r="X21" s="474" t="n"/>
+      <c r="Y21" s="474" t="n"/>
+      <c r="Z21" s="474" t="n"/>
+      <c r="AA21" s="474" t="n"/>
+      <c r="AB21" s="474" t="n"/>
+      <c r="AC21" s="474" t="n"/>
+      <c r="AD21" s="474" t="n"/>
+      <c r="AE21" s="474" t="n"/>
+      <c r="AF21" s="474" t="n"/>
+      <c r="AG21" s="474" t="n"/>
+      <c r="AH21" s="474" t="n"/>
+      <c r="AI21" s="474" t="n"/>
+      <c r="AJ21" s="474" t="n"/>
+      <c r="AK21" s="474" t="n"/>
+      <c r="AL21" s="474" t="n"/>
+      <c r="AM21" s="474" t="n"/>
+      <c r="AN21" s="479" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1" s="264">
-      <c r="A22" s="496" t="n"/>
+      <c r="A22" s="495" t="n"/>
       <c r="B22" s="481" t="n"/>
       <c r="C22" s="481" t="n"/>
       <c r="D22" s="481" t="n"/>
@@ -6444,139 +6426,135 @@
       <c r="AN22" s="486" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1" s="264">
-      <c r="A23" s="498" t="n"/>
-      <c r="B23" s="488" t="n"/>
-      <c r="C23" s="488" t="n"/>
-      <c r="D23" s="488" t="n"/>
-      <c r="E23" s="488" t="n"/>
-      <c r="F23" s="488" t="n"/>
-      <c r="G23" s="488" t="n"/>
-      <c r="H23" s="488" t="n"/>
-      <c r="I23" s="488" t="n"/>
-      <c r="J23" s="488" t="n"/>
-      <c r="K23" s="488" t="n"/>
-      <c r="L23" s="488" t="n"/>
-      <c r="M23" s="488" t="n"/>
-      <c r="N23" s="488" t="n"/>
-      <c r="O23" s="488" t="n"/>
-      <c r="P23" s="488" t="n"/>
-      <c r="Q23" s="488" t="n"/>
-      <c r="R23" s="488" t="n"/>
-      <c r="S23" s="488" t="n"/>
-      <c r="T23" s="488" t="n"/>
-      <c r="U23" s="488" t="n"/>
-      <c r="V23" s="488" t="n"/>
-      <c r="W23" s="488" t="n"/>
-      <c r="X23" s="488" t="n"/>
-      <c r="Y23" s="488" t="n"/>
-      <c r="Z23" s="488" t="n"/>
-      <c r="AA23" s="488" t="n"/>
-      <c r="AB23" s="488" t="n"/>
-      <c r="AC23" s="488" t="n"/>
-      <c r="AD23" s="488" t="n"/>
-      <c r="AE23" s="488" t="n"/>
-      <c r="AF23" s="488" t="n"/>
-      <c r="AG23" s="488" t="n"/>
-      <c r="AH23" s="488" t="n"/>
-      <c r="AI23" s="488" t="n"/>
-      <c r="AJ23" s="488" t="n"/>
-      <c r="AK23" s="488" t="n"/>
-      <c r="AL23" s="488" t="n"/>
-      <c r="AM23" s="488" t="n"/>
-      <c r="AN23" s="493" t="n"/>
+      <c r="A23" s="497" t="n"/>
+      <c r="B23" s="481" t="n"/>
+      <c r="C23" s="481" t="n"/>
+      <c r="D23" s="481" t="n"/>
+      <c r="E23" s="481" t="n"/>
+      <c r="F23" s="481" t="n"/>
+      <c r="G23" s="481" t="n"/>
+      <c r="H23" s="481" t="n"/>
+      <c r="I23" s="481" t="n"/>
+      <c r="J23" s="481" t="n"/>
+      <c r="K23" s="481" t="n"/>
+      <c r="L23" s="481" t="n"/>
+      <c r="M23" s="481" t="n"/>
+      <c r="N23" s="481" t="n"/>
+      <c r="O23" s="481" t="n"/>
+      <c r="P23" s="481" t="n"/>
+      <c r="Q23" s="481" t="n"/>
+      <c r="R23" s="481" t="n"/>
+      <c r="S23" s="481" t="n"/>
+      <c r="T23" s="481" t="n"/>
+      <c r="U23" s="481" t="n"/>
+      <c r="V23" s="481" t="n"/>
+      <c r="W23" s="481" t="n"/>
+      <c r="X23" s="481" t="n"/>
+      <c r="Y23" s="481" t="n"/>
+      <c r="Z23" s="481" t="n"/>
+      <c r="AA23" s="481" t="n"/>
+      <c r="AB23" s="481" t="n"/>
+      <c r="AC23" s="481" t="n"/>
+      <c r="AD23" s="481" t="n"/>
+      <c r="AE23" s="481" t="n"/>
+      <c r="AF23" s="481" t="n"/>
+      <c r="AG23" s="481" t="n"/>
+      <c r="AH23" s="481" t="n"/>
+      <c r="AI23" s="481" t="n"/>
+      <c r="AJ23" s="481" t="n"/>
+      <c r="AK23" s="481" t="n"/>
+      <c r="AL23" s="481" t="n"/>
+      <c r="AM23" s="481" t="n"/>
+      <c r="AN23" s="486" t="n"/>
     </row>
-    <row r="24" ht="4" customHeight="1" s="264">
-      <c r="A24" s="530" t="n"/>
-      <c r="B24" s="26" t="n"/>
-      <c r="C24" s="26" t="n"/>
-      <c r="D24" s="26" t="n"/>
-      <c r="E24" s="26" t="n"/>
-      <c r="F24" s="26" t="n"/>
-      <c r="G24" s="26" t="n"/>
-      <c r="H24" s="26" t="n"/>
-      <c r="I24" s="26" t="n"/>
-      <c r="J24" s="26" t="n"/>
-      <c r="K24" s="26" t="n"/>
-      <c r="L24" s="26" t="n"/>
-      <c r="M24" s="26" t="n"/>
-      <c r="N24" s="26" t="n"/>
-      <c r="O24" s="26" t="n"/>
-      <c r="P24" s="26" t="n"/>
-      <c r="Q24" s="26" t="n"/>
-      <c r="R24" s="26" t="n"/>
-      <c r="S24" s="26" t="n"/>
-      <c r="T24" s="26" t="n"/>
-      <c r="U24" s="26" t="n"/>
-      <c r="V24" s="26" t="n"/>
-      <c r="W24" s="26" t="n"/>
-      <c r="X24" s="26" t="n"/>
-      <c r="Y24" s="26" t="n"/>
-      <c r="Z24" s="26" t="n"/>
-      <c r="AA24" s="26" t="n"/>
-      <c r="AB24" s="26" t="n"/>
-      <c r="AC24" s="26" t="n"/>
-      <c r="AD24" s="26" t="n"/>
-      <c r="AE24" s="26" t="n"/>
-      <c r="AF24" s="26" t="n"/>
-      <c r="AG24" s="26" t="n"/>
-      <c r="AH24" s="26" t="n"/>
-      <c r="AI24" s="26" t="n"/>
-      <c r="AJ24" s="26" t="n"/>
-      <c r="AK24" s="26" t="n"/>
-      <c r="AL24" s="26" t="n"/>
-      <c r="AM24" s="26" t="n"/>
-      <c r="AN24" s="26" t="n"/>
+    <row r="24" ht="20" customHeight="1" s="264">
+      <c r="A24" s="496" t="n"/>
+      <c r="B24" s="488" t="n"/>
+      <c r="C24" s="488" t="n"/>
+      <c r="D24" s="488" t="n"/>
+      <c r="E24" s="488" t="n"/>
+      <c r="F24" s="488" t="n"/>
+      <c r="G24" s="488" t="n"/>
+      <c r="H24" s="488" t="n"/>
+      <c r="I24" s="488" t="n"/>
+      <c r="J24" s="488" t="n"/>
+      <c r="K24" s="488" t="n"/>
+      <c r="L24" s="488" t="n"/>
+      <c r="M24" s="488" t="n"/>
+      <c r="N24" s="488" t="n"/>
+      <c r="O24" s="488" t="n"/>
+      <c r="P24" s="488" t="n"/>
+      <c r="Q24" s="488" t="n"/>
+      <c r="R24" s="488" t="n"/>
+      <c r="S24" s="488" t="n"/>
+      <c r="T24" s="488" t="n"/>
+      <c r="U24" s="488" t="n"/>
+      <c r="V24" s="488" t="n"/>
+      <c r="W24" s="488" t="n"/>
+      <c r="X24" s="488" t="n"/>
+      <c r="Y24" s="488" t="n"/>
+      <c r="Z24" s="488" t="n"/>
+      <c r="AA24" s="488" t="n"/>
+      <c r="AB24" s="488" t="n"/>
+      <c r="AC24" s="488" t="n"/>
+      <c r="AD24" s="488" t="n"/>
+      <c r="AE24" s="488" t="n"/>
+      <c r="AF24" s="488" t="n"/>
+      <c r="AG24" s="488" t="n"/>
+      <c r="AH24" s="488" t="n"/>
+      <c r="AI24" s="488" t="n"/>
+      <c r="AJ24" s="488" t="n"/>
+      <c r="AK24" s="488" t="n"/>
+      <c r="AL24" s="488" t="n"/>
+      <c r="AM24" s="488" t="n"/>
+      <c r="AN24" s="493" t="n"/>
     </row>
-    <row r="25" ht="17" customHeight="1" s="264">
-      <c r="A25" s="470" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  3.  SPECIAL TOOLING / RE-INSPECTION</t>
-        </is>
-      </c>
-      <c r="B25" s="471" t="n"/>
-      <c r="C25" s="471" t="n"/>
-      <c r="D25" s="471" t="n"/>
-      <c r="E25" s="471" t="n"/>
-      <c r="F25" s="471" t="n"/>
-      <c r="G25" s="471" t="n"/>
-      <c r="H25" s="471" t="n"/>
-      <c r="I25" s="471" t="n"/>
-      <c r="J25" s="471" t="n"/>
-      <c r="K25" s="471" t="n"/>
-      <c r="L25" s="471" t="n"/>
-      <c r="M25" s="471" t="n"/>
-      <c r="N25" s="471" t="n"/>
-      <c r="O25" s="471" t="n"/>
-      <c r="P25" s="471" t="n"/>
-      <c r="Q25" s="471" t="n"/>
-      <c r="R25" s="471" t="n"/>
-      <c r="S25" s="471" t="n"/>
-      <c r="T25" s="471" t="n"/>
-      <c r="U25" s="471" t="n"/>
-      <c r="V25" s="471" t="n"/>
-      <c r="W25" s="471" t="n"/>
-      <c r="X25" s="471" t="n"/>
-      <c r="Y25" s="471" t="n"/>
-      <c r="Z25" s="471" t="n"/>
-      <c r="AA25" s="471" t="n"/>
-      <c r="AB25" s="471" t="n"/>
-      <c r="AC25" s="471" t="n"/>
-      <c r="AD25" s="471" t="n"/>
-      <c r="AE25" s="471" t="n"/>
-      <c r="AF25" s="471" t="n"/>
-      <c r="AG25" s="471" t="n"/>
-      <c r="AH25" s="471" t="n"/>
-      <c r="AI25" s="471" t="n"/>
-      <c r="AJ25" s="471" t="n"/>
-      <c r="AK25" s="471" t="n"/>
-      <c r="AL25" s="471" t="n"/>
-      <c r="AM25" s="471" t="n"/>
-      <c r="AN25" s="472" t="n"/>
+    <row r="25" ht="4" customHeight="1" s="264">
+      <c r="A25" s="523" t="n"/>
+      <c r="B25" s="26" t="n"/>
+      <c r="C25" s="26" t="n"/>
+      <c r="D25" s="26" t="n"/>
+      <c r="E25" s="26" t="n"/>
+      <c r="F25" s="26" t="n"/>
+      <c r="G25" s="26" t="n"/>
+      <c r="H25" s="26" t="n"/>
+      <c r="I25" s="26" t="n"/>
+      <c r="J25" s="26" t="n"/>
+      <c r="K25" s="26" t="n"/>
+      <c r="L25" s="26" t="n"/>
+      <c r="M25" s="26" t="n"/>
+      <c r="N25" s="26" t="n"/>
+      <c r="O25" s="26" t="n"/>
+      <c r="P25" s="26" t="n"/>
+      <c r="Q25" s="26" t="n"/>
+      <c r="R25" s="26" t="n"/>
+      <c r="S25" s="26" t="n"/>
+      <c r="T25" s="26" t="n"/>
+      <c r="U25" s="26" t="n"/>
+      <c r="V25" s="26" t="n"/>
+      <c r="W25" s="26" t="n"/>
+      <c r="X25" s="26" t="n"/>
+      <c r="Y25" s="26" t="n"/>
+      <c r="Z25" s="26" t="n"/>
+      <c r="AA25" s="26" t="n"/>
+      <c r="AB25" s="26" t="n"/>
+      <c r="AC25" s="26" t="n"/>
+      <c r="AD25" s="26" t="n"/>
+      <c r="AE25" s="26" t="n"/>
+      <c r="AF25" s="26" t="n"/>
+      <c r="AG25" s="26" t="n"/>
+      <c r="AH25" s="26" t="n"/>
+      <c r="AI25" s="26" t="n"/>
+      <c r="AJ25" s="26" t="n"/>
+      <c r="AK25" s="26" t="n"/>
+      <c r="AL25" s="26" t="n"/>
+      <c r="AM25" s="26" t="n"/>
+      <c r="AN25" s="26" t="n"/>
     </row>
-    <row r="26" ht="20" customHeight="1" s="264">
-      <c r="A26" s="499" t="inlineStr">
-        <is>
-          <t>Special Tooling / Process</t>
+    <row r="26" ht="17" customHeight="1" s="264">
+      <c r="A26" s="470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4.  POST-REWORK VERIFICATION</t>
         </is>
       </c>
       <c r="B26" s="471" t="n"/>
@@ -6584,8 +6562,8 @@
       <c r="D26" s="471" t="n"/>
       <c r="E26" s="471" t="n"/>
       <c r="F26" s="471" t="n"/>
-      <c r="G26" s="500" t="n"/>
-      <c r="H26" s="501" t="n"/>
+      <c r="G26" s="471" t="n"/>
+      <c r="H26" s="471" t="n"/>
       <c r="I26" s="471" t="n"/>
       <c r="J26" s="471" t="n"/>
       <c r="K26" s="471" t="n"/>
@@ -6597,19 +6575,15 @@
       <c r="Q26" s="471" t="n"/>
       <c r="R26" s="471" t="n"/>
       <c r="S26" s="471" t="n"/>
-      <c r="T26" s="500" t="n"/>
-      <c r="U26" s="502" t="inlineStr">
-        <is>
-          <t>Re-Inspection Required (Y/N)</t>
-        </is>
-      </c>
+      <c r="T26" s="471" t="n"/>
+      <c r="U26" s="471" t="n"/>
       <c r="V26" s="471" t="n"/>
       <c r="W26" s="471" t="n"/>
       <c r="X26" s="471" t="n"/>
       <c r="Y26" s="471" t="n"/>
       <c r="Z26" s="471" t="n"/>
-      <c r="AA26" s="500" t="n"/>
-      <c r="AB26" s="503" t="n"/>
+      <c r="AA26" s="471" t="n"/>
+      <c r="AB26" s="471" t="n"/>
       <c r="AC26" s="471" t="n"/>
       <c r="AD26" s="471" t="n"/>
       <c r="AE26" s="471" t="n"/>
@@ -6623,176 +6597,202 @@
       <c r="AM26" s="471" t="n"/>
       <c r="AN26" s="472" t="n"/>
     </row>
-    <row r="27" ht="4" customHeight="1" s="264">
-      <c r="A27" s="530" t="n"/>
-      <c r="B27" s="26" t="n"/>
-      <c r="C27" s="26" t="n"/>
-      <c r="D27" s="26" t="n"/>
-      <c r="E27" s="26" t="n"/>
-      <c r="F27" s="26" t="n"/>
-      <c r="G27" s="26" t="n"/>
-      <c r="H27" s="26" t="n"/>
-      <c r="I27" s="26" t="n"/>
-      <c r="J27" s="26" t="n"/>
-      <c r="K27" s="26" t="n"/>
-      <c r="L27" s="26" t="n"/>
-      <c r="M27" s="26" t="n"/>
-      <c r="N27" s="26" t="n"/>
-      <c r="O27" s="26" t="n"/>
-      <c r="P27" s="26" t="n"/>
-      <c r="Q27" s="26" t="n"/>
-      <c r="R27" s="26" t="n"/>
-      <c r="S27" s="26" t="n"/>
-      <c r="T27" s="26" t="n"/>
-      <c r="U27" s="26" t="n"/>
-      <c r="V27" s="26" t="n"/>
-      <c r="W27" s="26" t="n"/>
-      <c r="X27" s="26" t="n"/>
-      <c r="Y27" s="26" t="n"/>
-      <c r="Z27" s="26" t="n"/>
-      <c r="AA27" s="26" t="n"/>
-      <c r="AB27" s="26" t="n"/>
-      <c r="AC27" s="26" t="n"/>
-      <c r="AD27" s="26" t="n"/>
-      <c r="AE27" s="26" t="n"/>
-      <c r="AF27" s="26" t="n"/>
-      <c r="AG27" s="26" t="n"/>
-      <c r="AH27" s="26" t="n"/>
-      <c r="AI27" s="26" t="n"/>
-      <c r="AJ27" s="26" t="n"/>
-      <c r="AK27" s="26" t="n"/>
-      <c r="AL27" s="26" t="n"/>
-      <c r="AM27" s="26" t="n"/>
-      <c r="AN27" s="26" t="n"/>
+    <row r="27" ht="17" customHeight="1" s="264">
+      <c r="A27" s="498" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B27" s="475" t="n"/>
+      <c r="C27" s="499" t="inlineStr">
+        <is>
+          <t>Cat.</t>
+        </is>
+      </c>
+      <c r="D27" s="474" t="n"/>
+      <c r="E27" s="475" t="n"/>
+      <c r="F27" s="499" t="inlineStr">
+        <is>
+          <t>Verification Item</t>
+        </is>
+      </c>
+      <c r="G27" s="474" t="n"/>
+      <c r="H27" s="474" t="n"/>
+      <c r="I27" s="474" t="n"/>
+      <c r="J27" s="474" t="n"/>
+      <c r="K27" s="474" t="n"/>
+      <c r="L27" s="474" t="n"/>
+      <c r="M27" s="474" t="n"/>
+      <c r="N27" s="474" t="n"/>
+      <c r="O27" s="474" t="n"/>
+      <c r="P27" s="474" t="n"/>
+      <c r="Q27" s="474" t="n"/>
+      <c r="R27" s="474" t="n"/>
+      <c r="S27" s="474" t="n"/>
+      <c r="T27" s="474" t="n"/>
+      <c r="U27" s="475" t="n"/>
+      <c r="V27" s="499" t="inlineStr">
+        <is>
+          <t>Acceptance Criteria</t>
+        </is>
+      </c>
+      <c r="W27" s="474" t="n"/>
+      <c r="X27" s="474" t="n"/>
+      <c r="Y27" s="474" t="n"/>
+      <c r="Z27" s="474" t="n"/>
+      <c r="AA27" s="474" t="n"/>
+      <c r="AB27" s="474" t="n"/>
+      <c r="AC27" s="474" t="n"/>
+      <c r="AD27" s="474" t="n"/>
+      <c r="AE27" s="475" t="n"/>
+      <c r="AF27" s="499" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="AG27" s="474" t="n"/>
+      <c r="AH27" s="474" t="n"/>
+      <c r="AI27" s="475" t="n"/>
+      <c r="AJ27" s="500" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="AK27" s="474" t="n"/>
+      <c r="AL27" s="474" t="n"/>
+      <c r="AM27" s="474" t="n"/>
+      <c r="AN27" s="479" t="n"/>
     </row>
-    <row r="28" ht="17" customHeight="1" s="264">
-      <c r="A28" s="470" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4.  POST-REWORK VERIFICATION</t>
-        </is>
-      </c>
-      <c r="B28" s="471" t="n"/>
-      <c r="C28" s="471" t="n"/>
-      <c r="D28" s="471" t="n"/>
-      <c r="E28" s="471" t="n"/>
-      <c r="F28" s="471" t="n"/>
-      <c r="G28" s="471" t="n"/>
-      <c r="H28" s="471" t="n"/>
-      <c r="I28" s="471" t="n"/>
-      <c r="J28" s="471" t="n"/>
-      <c r="K28" s="471" t="n"/>
-      <c r="L28" s="471" t="n"/>
-      <c r="M28" s="471" t="n"/>
-      <c r="N28" s="471" t="n"/>
-      <c r="O28" s="471" t="n"/>
-      <c r="P28" s="471" t="n"/>
-      <c r="Q28" s="471" t="n"/>
-      <c r="R28" s="471" t="n"/>
-      <c r="S28" s="471" t="n"/>
-      <c r="T28" s="471" t="n"/>
-      <c r="U28" s="471" t="n"/>
-      <c r="V28" s="471" t="n"/>
-      <c r="W28" s="471" t="n"/>
-      <c r="X28" s="471" t="n"/>
-      <c r="Y28" s="471" t="n"/>
-      <c r="Z28" s="471" t="n"/>
-      <c r="AA28" s="471" t="n"/>
-      <c r="AB28" s="471" t="n"/>
-      <c r="AC28" s="471" t="n"/>
-      <c r="AD28" s="471" t="n"/>
-      <c r="AE28" s="471" t="n"/>
-      <c r="AF28" s="471" t="n"/>
-      <c r="AG28" s="471" t="n"/>
-      <c r="AH28" s="471" t="n"/>
-      <c r="AI28" s="471" t="n"/>
-      <c r="AJ28" s="471" t="n"/>
-      <c r="AK28" s="471" t="n"/>
-      <c r="AL28" s="471" t="n"/>
-      <c r="AM28" s="471" t="n"/>
-      <c r="AN28" s="472" t="n"/>
+    <row r="28" ht="20" customHeight="1" s="264">
+      <c r="A28" s="501">
+        <f>ROW()-ROW($A$28)+1</f>
+        <v/>
+      </c>
+      <c r="B28" s="482" t="n"/>
+      <c r="C28" s="502" t="inlineStr">
+        <is>
+          <t>OPS</t>
+        </is>
+      </c>
+      <c r="D28" s="481" t="n"/>
+      <c r="E28" s="482" t="n"/>
+      <c r="F28" s="503" t="inlineStr">
+        <is>
+          <t>Rework performed per the approved method only.</t>
+        </is>
+      </c>
+      <c r="G28" s="481" t="n"/>
+      <c r="H28" s="481" t="n"/>
+      <c r="I28" s="481" t="n"/>
+      <c r="J28" s="481" t="n"/>
+      <c r="K28" s="481" t="n"/>
+      <c r="L28" s="481" t="n"/>
+      <c r="M28" s="481" t="n"/>
+      <c r="N28" s="481" t="n"/>
+      <c r="O28" s="481" t="n"/>
+      <c r="P28" s="481" t="n"/>
+      <c r="Q28" s="481" t="n"/>
+      <c r="R28" s="481" t="n"/>
+      <c r="S28" s="481" t="n"/>
+      <c r="T28" s="481" t="n"/>
+      <c r="U28" s="482" t="n"/>
+      <c r="V28" s="504" t="inlineStr">
+        <is>
+          <t>No undocumented deviation from method.</t>
+        </is>
+      </c>
+      <c r="W28" s="481" t="n"/>
+      <c r="X28" s="481" t="n"/>
+      <c r="Y28" s="481" t="n"/>
+      <c r="Z28" s="481" t="n"/>
+      <c r="AA28" s="481" t="n"/>
+      <c r="AB28" s="481" t="n"/>
+      <c r="AC28" s="481" t="n"/>
+      <c r="AD28" s="481" t="n"/>
+      <c r="AE28" s="482" t="n"/>
+      <c r="AF28" s="505" t="n"/>
+      <c r="AG28" s="481" t="n"/>
+      <c r="AH28" s="481" t="n"/>
+      <c r="AI28" s="482" t="n"/>
+      <c r="AJ28" s="506" t="n"/>
+      <c r="AK28" s="481" t="n"/>
+      <c r="AL28" s="481" t="n"/>
+      <c r="AM28" s="481" t="n"/>
+      <c r="AN28" s="486" t="n"/>
     </row>
-    <row r="29" ht="17" customHeight="1" s="264">
-      <c r="A29" s="504" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B29" s="475" t="n"/>
-      <c r="C29" s="505" t="inlineStr">
-        <is>
-          <t>Cat.</t>
-        </is>
-      </c>
-      <c r="D29" s="474" t="n"/>
-      <c r="E29" s="475" t="n"/>
-      <c r="F29" s="505" t="inlineStr">
-        <is>
-          <t>Post-Rework Verification Item</t>
-        </is>
-      </c>
-      <c r="G29" s="474" t="n"/>
-      <c r="H29" s="474" t="n"/>
-      <c r="I29" s="474" t="n"/>
-      <c r="J29" s="474" t="n"/>
-      <c r="K29" s="474" t="n"/>
-      <c r="L29" s="474" t="n"/>
-      <c r="M29" s="474" t="n"/>
-      <c r="N29" s="474" t="n"/>
-      <c r="O29" s="474" t="n"/>
-      <c r="P29" s="474" t="n"/>
-      <c r="Q29" s="474" t="n"/>
-      <c r="R29" s="474" t="n"/>
-      <c r="S29" s="474" t="n"/>
-      <c r="T29" s="474" t="n"/>
-      <c r="U29" s="475" t="n"/>
-      <c r="V29" s="505" t="inlineStr">
-        <is>
-          <t>Acceptance / Control Rule</t>
-        </is>
-      </c>
-      <c r="W29" s="474" t="n"/>
-      <c r="X29" s="474" t="n"/>
-      <c r="Y29" s="474" t="n"/>
-      <c r="Z29" s="474" t="n"/>
-      <c r="AA29" s="474" t="n"/>
-      <c r="AB29" s="474" t="n"/>
-      <c r="AC29" s="474" t="n"/>
-      <c r="AD29" s="474" t="n"/>
-      <c r="AE29" s="475" t="n"/>
-      <c r="AF29" s="505" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="AG29" s="474" t="n"/>
-      <c r="AH29" s="474" t="n"/>
-      <c r="AI29" s="475" t="n"/>
-      <c r="AJ29" s="506" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="AK29" s="474" t="n"/>
-      <c r="AL29" s="474" t="n"/>
-      <c r="AM29" s="474" t="n"/>
-      <c r="AN29" s="479" t="n"/>
+    <row r="29" ht="20" customHeight="1" s="264">
+      <c r="A29" s="501">
+        <f>ROW()-ROW($A$28)+1</f>
+        <v/>
+      </c>
+      <c r="B29" s="482" t="n"/>
+      <c r="C29" s="507" t="inlineStr">
+        <is>
+          <t>QUA</t>
+        </is>
+      </c>
+      <c r="D29" s="481" t="n"/>
+      <c r="E29" s="482" t="n"/>
+      <c r="F29" s="508" t="inlineStr">
+        <is>
+          <t>Reworked features re-measured on CTQ characteristics.</t>
+        </is>
+      </c>
+      <c r="G29" s="481" t="n"/>
+      <c r="H29" s="481" t="n"/>
+      <c r="I29" s="481" t="n"/>
+      <c r="J29" s="481" t="n"/>
+      <c r="K29" s="481" t="n"/>
+      <c r="L29" s="481" t="n"/>
+      <c r="M29" s="481" t="n"/>
+      <c r="N29" s="481" t="n"/>
+      <c r="O29" s="481" t="n"/>
+      <c r="P29" s="481" t="n"/>
+      <c r="Q29" s="481" t="n"/>
+      <c r="R29" s="481" t="n"/>
+      <c r="S29" s="481" t="n"/>
+      <c r="T29" s="481" t="n"/>
+      <c r="U29" s="482" t="n"/>
+      <c r="V29" s="504" t="inlineStr">
+        <is>
+          <t>Dimensions logged on FRM-622.</t>
+        </is>
+      </c>
+      <c r="W29" s="481" t="n"/>
+      <c r="X29" s="481" t="n"/>
+      <c r="Y29" s="481" t="n"/>
+      <c r="Z29" s="481" t="n"/>
+      <c r="AA29" s="481" t="n"/>
+      <c r="AB29" s="481" t="n"/>
+      <c r="AC29" s="481" t="n"/>
+      <c r="AD29" s="481" t="n"/>
+      <c r="AE29" s="482" t="n"/>
+      <c r="AF29" s="505" t="n"/>
+      <c r="AG29" s="481" t="n"/>
+      <c r="AH29" s="481" t="n"/>
+      <c r="AI29" s="482" t="n"/>
+      <c r="AJ29" s="506" t="n"/>
+      <c r="AK29" s="481" t="n"/>
+      <c r="AL29" s="481" t="n"/>
+      <c r="AM29" s="481" t="n"/>
+      <c r="AN29" s="486" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1" s="264">
-      <c r="A30" s="507">
-        <f>ROW()-ROW($A$30)+1</f>
+      <c r="A30" s="501">
+        <f>ROW()-ROW($A$28)+1</f>
         <v/>
       </c>
       <c r="B30" s="482" t="n"/>
-      <c r="C30" s="508" t="inlineStr">
-        <is>
-          <t>OPS</t>
+      <c r="C30" s="507" t="inlineStr">
+        <is>
+          <t>QUA</t>
         </is>
       </c>
       <c r="D30" s="481" t="n"/>
       <c r="E30" s="482" t="n"/>
-      <c r="F30" s="509" t="inlineStr">
-        <is>
-          <t>Rework performed per the approved method only.</t>
+      <c r="F30" s="503" t="inlineStr">
+        <is>
+          <t>All re-measured features within drawing tolerance.</t>
         </is>
       </c>
       <c r="G30" s="481" t="n"/>
@@ -6810,9 +6810,9 @@
       <c r="S30" s="481" t="n"/>
       <c r="T30" s="481" t="n"/>
       <c r="U30" s="482" t="n"/>
-      <c r="V30" s="510" t="inlineStr">
-        <is>
-          <t>No undocumented deviation from method.</t>
+      <c r="V30" s="504" t="inlineStr">
+        <is>
+          <t>No characteristic out of limit.</t>
         </is>
       </c>
       <c r="W30" s="481" t="n"/>
@@ -6824,32 +6824,32 @@
       <c r="AC30" s="481" t="n"/>
       <c r="AD30" s="481" t="n"/>
       <c r="AE30" s="482" t="n"/>
-      <c r="AF30" s="511" t="n"/>
+      <c r="AF30" s="505" t="n"/>
       <c r="AG30" s="481" t="n"/>
       <c r="AH30" s="481" t="n"/>
       <c r="AI30" s="482" t="n"/>
-      <c r="AJ30" s="512" t="n"/>
+      <c r="AJ30" s="506" t="n"/>
       <c r="AK30" s="481" t="n"/>
       <c r="AL30" s="481" t="n"/>
       <c r="AM30" s="481" t="n"/>
       <c r="AN30" s="486" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1" s="264">
-      <c r="A31" s="507">
-        <f>ROW()-ROW($A$30)+1</f>
+      <c r="A31" s="501">
+        <f>ROW()-ROW($A$28)+1</f>
         <v/>
       </c>
       <c r="B31" s="482" t="n"/>
-      <c r="C31" s="513" t="inlineStr">
+      <c r="C31" s="507" t="inlineStr">
         <is>
           <t>QUA</t>
         </is>
       </c>
       <c r="D31" s="481" t="n"/>
       <c r="E31" s="482" t="n"/>
-      <c r="F31" s="514" t="inlineStr">
-        <is>
-          <t>Reworked features re-measured on CTQ characteristics.</t>
+      <c r="F31" s="508" t="inlineStr">
+        <is>
+          <t>Adjacent / dependent features not degraded.</t>
         </is>
       </c>
       <c r="G31" s="481" t="n"/>
@@ -6867,9 +6867,9 @@
       <c r="S31" s="481" t="n"/>
       <c r="T31" s="481" t="n"/>
       <c r="U31" s="482" t="n"/>
-      <c r="V31" s="510" t="inlineStr">
-        <is>
-          <t>Dimensions logged on FRM-622.</t>
+      <c r="V31" s="504" t="inlineStr">
+        <is>
+          <t>Form, finish and GD&amp;T re-verified.</t>
         </is>
       </c>
       <c r="W31" s="481" t="n"/>
@@ -6881,32 +6881,32 @@
       <c r="AC31" s="481" t="n"/>
       <c r="AD31" s="481" t="n"/>
       <c r="AE31" s="482" t="n"/>
-      <c r="AF31" s="511" t="n"/>
+      <c r="AF31" s="505" t="n"/>
       <c r="AG31" s="481" t="n"/>
       <c r="AH31" s="481" t="n"/>
       <c r="AI31" s="482" t="n"/>
-      <c r="AJ31" s="512" t="n"/>
+      <c r="AJ31" s="506" t="n"/>
       <c r="AK31" s="481" t="n"/>
       <c r="AL31" s="481" t="n"/>
       <c r="AM31" s="481" t="n"/>
       <c r="AN31" s="486" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1" s="264">
-      <c r="A32" s="507">
-        <f>ROW()-ROW($A$30)+1</f>
+      <c r="A32" s="501">
+        <f>ROW()-ROW($A$28)+1</f>
         <v/>
       </c>
       <c r="B32" s="482" t="n"/>
-      <c r="C32" s="513" t="inlineStr">
+      <c r="C32" s="507" t="inlineStr">
         <is>
           <t>QUA</t>
         </is>
       </c>
       <c r="D32" s="481" t="n"/>
       <c r="E32" s="482" t="n"/>
-      <c r="F32" s="509" t="inlineStr">
-        <is>
-          <t>All re-measured features within drawing tolerance.</t>
+      <c r="F32" s="503" t="inlineStr">
+        <is>
+          <t>Surface finish and edges acceptable after rework.</t>
         </is>
       </c>
       <c r="G32" s="481" t="n"/>
@@ -6924,9 +6924,9 @@
       <c r="S32" s="481" t="n"/>
       <c r="T32" s="481" t="n"/>
       <c r="U32" s="482" t="n"/>
-      <c r="V32" s="510" t="inlineStr">
-        <is>
-          <t>No characteristic out of limit.</t>
+      <c r="V32" s="504" t="inlineStr">
+        <is>
+          <t>Visual + Ra check per drawing.</t>
         </is>
       </c>
       <c r="W32" s="481" t="n"/>
@@ -6938,32 +6938,32 @@
       <c r="AC32" s="481" t="n"/>
       <c r="AD32" s="481" t="n"/>
       <c r="AE32" s="482" t="n"/>
-      <c r="AF32" s="511" t="n"/>
+      <c r="AF32" s="505" t="n"/>
       <c r="AG32" s="481" t="n"/>
       <c r="AH32" s="481" t="n"/>
       <c r="AI32" s="482" t="n"/>
-      <c r="AJ32" s="512" t="n"/>
+      <c r="AJ32" s="506" t="n"/>
       <c r="AK32" s="481" t="n"/>
       <c r="AL32" s="481" t="n"/>
       <c r="AM32" s="481" t="n"/>
       <c r="AN32" s="486" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1" s="264">
-      <c r="A33" s="507">
-        <f>ROW()-ROW($A$30)+1</f>
+      <c r="A33" s="501">
+        <f>ROW()-ROW($A$28)+1</f>
         <v/>
       </c>
       <c r="B33" s="482" t="n"/>
-      <c r="C33" s="513" t="inlineStr">
-        <is>
-          <t>QUA</t>
+      <c r="C33" s="502" t="inlineStr">
+        <is>
+          <t>DOC</t>
         </is>
       </c>
       <c r="D33" s="481" t="n"/>
       <c r="E33" s="482" t="n"/>
-      <c r="F33" s="514" t="inlineStr">
-        <is>
-          <t>Adjacent / dependent features not degraded by rework.</t>
+      <c r="F33" s="508" t="inlineStr">
+        <is>
+          <t>Rework evidence attached to the job dossier.</t>
         </is>
       </c>
       <c r="G33" s="481" t="n"/>
@@ -6981,9 +6981,9 @@
       <c r="S33" s="481" t="n"/>
       <c r="T33" s="481" t="n"/>
       <c r="U33" s="482" t="n"/>
-      <c r="V33" s="510" t="inlineStr">
-        <is>
-          <t>Form, finish and GD&amp;T re-verified.</t>
+      <c r="V33" s="504" t="inlineStr">
+        <is>
+          <t>Photos / reports linked to FRM-205.</t>
         </is>
       </c>
       <c r="W33" s="481" t="n"/>
@@ -6995,32 +6995,32 @@
       <c r="AC33" s="481" t="n"/>
       <c r="AD33" s="481" t="n"/>
       <c r="AE33" s="482" t="n"/>
-      <c r="AF33" s="511" t="n"/>
+      <c r="AF33" s="505" t="n"/>
       <c r="AG33" s="481" t="n"/>
       <c r="AH33" s="481" t="n"/>
       <c r="AI33" s="482" t="n"/>
-      <c r="AJ33" s="512" t="n"/>
+      <c r="AJ33" s="506" t="n"/>
       <c r="AK33" s="481" t="n"/>
       <c r="AL33" s="481" t="n"/>
       <c r="AM33" s="481" t="n"/>
       <c r="AN33" s="486" t="n"/>
     </row>
     <row r="34" ht="20" customHeight="1" s="264">
-      <c r="A34" s="507">
-        <f>ROW()-ROW($A$30)+1</f>
+      <c r="A34" s="501">
+        <f>ROW()-ROW($A$28)+1</f>
         <v/>
       </c>
       <c r="B34" s="482" t="n"/>
-      <c r="C34" s="508" t="inlineStr">
-        <is>
-          <t>DOC</t>
+      <c r="C34" s="502" t="inlineStr">
+        <is>
+          <t>OPS</t>
         </is>
       </c>
       <c r="D34" s="481" t="n"/>
       <c r="E34" s="482" t="n"/>
-      <c r="F34" s="509" t="inlineStr">
-        <is>
-          <t>Rework evidence attached to the job dossier.</t>
+      <c r="F34" s="503" t="inlineStr">
+        <is>
+          <t>NCR updated and disposition closed.</t>
         </is>
       </c>
       <c r="G34" s="481" t="n"/>
@@ -7038,9 +7038,9 @@
       <c r="S34" s="481" t="n"/>
       <c r="T34" s="481" t="n"/>
       <c r="U34" s="482" t="n"/>
-      <c r="V34" s="510" t="inlineStr">
-        <is>
-          <t>Photos / reports linked to FRM-205.</t>
+      <c r="V34" s="504" t="inlineStr">
+        <is>
+          <t>FRM-651 status reconciled.</t>
         </is>
       </c>
       <c r="W34" s="481" t="n"/>
@@ -7052,760 +7052,607 @@
       <c r="AC34" s="481" t="n"/>
       <c r="AD34" s="481" t="n"/>
       <c r="AE34" s="482" t="n"/>
-      <c r="AF34" s="511" t="n"/>
+      <c r="AF34" s="505" t="n"/>
       <c r="AG34" s="481" t="n"/>
       <c r="AH34" s="481" t="n"/>
       <c r="AI34" s="482" t="n"/>
-      <c r="AJ34" s="512" t="n"/>
+      <c r="AJ34" s="506" t="n"/>
       <c r="AK34" s="481" t="n"/>
       <c r="AL34" s="481" t="n"/>
       <c r="AM34" s="481" t="n"/>
       <c r="AN34" s="486" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1" s="264">
-      <c r="A35" s="507">
-        <f>ROW()-ROW($A$30)+1</f>
+      <c r="A35" s="509">
+        <f>ROW()-ROW($A$28)+1</f>
         <v/>
       </c>
-      <c r="B35" s="482" t="n"/>
-      <c r="C35" s="508" t="inlineStr">
+      <c r="B35" s="489" t="n"/>
+      <c r="C35" s="510" t="inlineStr">
         <is>
           <t>OPS</t>
         </is>
       </c>
-      <c r="D35" s="481" t="n"/>
-      <c r="E35" s="482" t="n"/>
-      <c r="F35" s="514" t="inlineStr">
-        <is>
-          <t>NCR updated and disposition closed.</t>
-        </is>
-      </c>
-      <c r="G35" s="481" t="n"/>
-      <c r="H35" s="481" t="n"/>
-      <c r="I35" s="481" t="n"/>
-      <c r="J35" s="481" t="n"/>
-      <c r="K35" s="481" t="n"/>
-      <c r="L35" s="481" t="n"/>
-      <c r="M35" s="481" t="n"/>
-      <c r="N35" s="481" t="n"/>
-      <c r="O35" s="481" t="n"/>
-      <c r="P35" s="481" t="n"/>
-      <c r="Q35" s="481" t="n"/>
-      <c r="R35" s="481" t="n"/>
-      <c r="S35" s="481" t="n"/>
-      <c r="T35" s="481" t="n"/>
-      <c r="U35" s="482" t="n"/>
-      <c r="V35" s="510" t="inlineStr">
-        <is>
-          <t>FRM-651 status reconciled.</t>
-        </is>
-      </c>
-      <c r="W35" s="481" t="n"/>
-      <c r="X35" s="481" t="n"/>
-      <c r="Y35" s="481" t="n"/>
-      <c r="Z35" s="481" t="n"/>
-      <c r="AA35" s="481" t="n"/>
-      <c r="AB35" s="481" t="n"/>
-      <c r="AC35" s="481" t="n"/>
-      <c r="AD35" s="481" t="n"/>
-      <c r="AE35" s="482" t="n"/>
-      <c r="AF35" s="511" t="n"/>
-      <c r="AG35" s="481" t="n"/>
-      <c r="AH35" s="481" t="n"/>
-      <c r="AI35" s="482" t="n"/>
-      <c r="AJ35" s="512" t="n"/>
-      <c r="AK35" s="481" t="n"/>
-      <c r="AL35" s="481" t="n"/>
-      <c r="AM35" s="481" t="n"/>
-      <c r="AN35" s="486" t="n"/>
+      <c r="D35" s="488" t="n"/>
+      <c r="E35" s="489" t="n"/>
+      <c r="F35" s="511" t="inlineStr">
+        <is>
+          <t>Tray status updated per WI-703.</t>
+        </is>
+      </c>
+      <c r="G35" s="488" t="n"/>
+      <c r="H35" s="488" t="n"/>
+      <c r="I35" s="488" t="n"/>
+      <c r="J35" s="488" t="n"/>
+      <c r="K35" s="488" t="n"/>
+      <c r="L35" s="488" t="n"/>
+      <c r="M35" s="488" t="n"/>
+      <c r="N35" s="488" t="n"/>
+      <c r="O35" s="488" t="n"/>
+      <c r="P35" s="488" t="n"/>
+      <c r="Q35" s="488" t="n"/>
+      <c r="R35" s="488" t="n"/>
+      <c r="S35" s="488" t="n"/>
+      <c r="T35" s="488" t="n"/>
+      <c r="U35" s="489" t="n"/>
+      <c r="V35" s="512" t="inlineStr">
+        <is>
+          <t>Yellow → Blue/Green if accepted; Red if scrap.</t>
+        </is>
+      </c>
+      <c r="W35" s="488" t="n"/>
+      <c r="X35" s="488" t="n"/>
+      <c r="Y35" s="488" t="n"/>
+      <c r="Z35" s="488" t="n"/>
+      <c r="AA35" s="488" t="n"/>
+      <c r="AB35" s="488" t="n"/>
+      <c r="AC35" s="488" t="n"/>
+      <c r="AD35" s="488" t="n"/>
+      <c r="AE35" s="489" t="n"/>
+      <c r="AF35" s="513" t="n"/>
+      <c r="AG35" s="488" t="n"/>
+      <c r="AH35" s="488" t="n"/>
+      <c r="AI35" s="489" t="n"/>
+      <c r="AJ35" s="514" t="n"/>
+      <c r="AK35" s="488" t="n"/>
+      <c r="AL35" s="488" t="n"/>
+      <c r="AM35" s="488" t="n"/>
+      <c r="AN35" s="493" t="n"/>
     </row>
-    <row r="36" ht="20" customHeight="1" s="264">
-      <c r="A36" s="507">
-        <f>ROW()-ROW($A$30)+1</f>
-        <v/>
-      </c>
-      <c r="B36" s="482" t="n"/>
-      <c r="C36" s="508" t="inlineStr">
-        <is>
-          <t>OPS</t>
-        </is>
-      </c>
-      <c r="D36" s="481" t="n"/>
-      <c r="E36" s="482" t="n"/>
-      <c r="F36" s="509" t="inlineStr">
-        <is>
-          <t>Tray status updated per WI-703.</t>
-        </is>
-      </c>
-      <c r="G36" s="481" t="n"/>
-      <c r="H36" s="481" t="n"/>
-      <c r="I36" s="481" t="n"/>
-      <c r="J36" s="481" t="n"/>
-      <c r="K36" s="481" t="n"/>
-      <c r="L36" s="481" t="n"/>
-      <c r="M36" s="481" t="n"/>
-      <c r="N36" s="481" t="n"/>
-      <c r="O36" s="481" t="n"/>
-      <c r="P36" s="481" t="n"/>
-      <c r="Q36" s="481" t="n"/>
-      <c r="R36" s="481" t="n"/>
-      <c r="S36" s="481" t="n"/>
-      <c r="T36" s="481" t="n"/>
-      <c r="U36" s="482" t="n"/>
-      <c r="V36" s="510" t="inlineStr">
-        <is>
-          <t>Yellow → Blue/Green if accepted; Red if scrap.</t>
-        </is>
-      </c>
-      <c r="W36" s="481" t="n"/>
-      <c r="X36" s="481" t="n"/>
-      <c r="Y36" s="481" t="n"/>
-      <c r="Z36" s="481" t="n"/>
-      <c r="AA36" s="481" t="n"/>
-      <c r="AB36" s="481" t="n"/>
-      <c r="AC36" s="481" t="n"/>
-      <c r="AD36" s="481" t="n"/>
-      <c r="AE36" s="482" t="n"/>
-      <c r="AF36" s="511" t="n"/>
-      <c r="AG36" s="481" t="n"/>
-      <c r="AH36" s="481" t="n"/>
-      <c r="AI36" s="482" t="n"/>
-      <c r="AJ36" s="512" t="n"/>
-      <c r="AK36" s="481" t="n"/>
-      <c r="AL36" s="481" t="n"/>
-      <c r="AM36" s="481" t="n"/>
-      <c r="AN36" s="486" t="n"/>
+    <row r="36" ht="4" customHeight="1" s="264">
+      <c r="A36" s="523" t="n"/>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+      <c r="E36" s="26" t="n"/>
+      <c r="F36" s="26" t="n"/>
+      <c r="G36" s="26" t="n"/>
+      <c r="H36" s="26" t="n"/>
+      <c r="I36" s="26" t="n"/>
+      <c r="J36" s="26" t="n"/>
+      <c r="K36" s="26" t="n"/>
+      <c r="L36" s="26" t="n"/>
+      <c r="M36" s="26" t="n"/>
+      <c r="N36" s="26" t="n"/>
+      <c r="O36" s="26" t="n"/>
+      <c r="P36" s="26" t="n"/>
+      <c r="Q36" s="26" t="n"/>
+      <c r="R36" s="26" t="n"/>
+      <c r="S36" s="26" t="n"/>
+      <c r="T36" s="26" t="n"/>
+      <c r="U36" s="26" t="n"/>
+      <c r="V36" s="26" t="n"/>
+      <c r="W36" s="26" t="n"/>
+      <c r="X36" s="26" t="n"/>
+      <c r="Y36" s="26" t="n"/>
+      <c r="Z36" s="26" t="n"/>
+      <c r="AA36" s="26" t="n"/>
+      <c r="AB36" s="26" t="n"/>
+      <c r="AC36" s="26" t="n"/>
+      <c r="AD36" s="26" t="n"/>
+      <c r="AE36" s="26" t="n"/>
+      <c r="AF36" s="26" t="n"/>
+      <c r="AG36" s="26" t="n"/>
+      <c r="AH36" s="26" t="n"/>
+      <c r="AI36" s="26" t="n"/>
+      <c r="AJ36" s="26" t="n"/>
+      <c r="AK36" s="26" t="n"/>
+      <c r="AL36" s="26" t="n"/>
+      <c r="AM36" s="26" t="n"/>
+      <c r="AN36" s="26" t="n"/>
     </row>
-    <row r="37" ht="20" customHeight="1" s="264">
-      <c r="A37" s="507">
-        <f>ROW()-ROW($A$30)+1</f>
-        <v/>
-      </c>
-      <c r="B37" s="482" t="n"/>
-      <c r="C37" s="515" t="n"/>
-      <c r="D37" s="481" t="n"/>
-      <c r="E37" s="482" t="n"/>
-      <c r="F37" s="516" t="n"/>
-      <c r="G37" s="481" t="n"/>
-      <c r="H37" s="481" t="n"/>
-      <c r="I37" s="481" t="n"/>
-      <c r="J37" s="481" t="n"/>
-      <c r="K37" s="481" t="n"/>
-      <c r="L37" s="481" t="n"/>
-      <c r="M37" s="481" t="n"/>
-      <c r="N37" s="481" t="n"/>
-      <c r="O37" s="481" t="n"/>
-      <c r="P37" s="481" t="n"/>
-      <c r="Q37" s="481" t="n"/>
-      <c r="R37" s="481" t="n"/>
-      <c r="S37" s="481" t="n"/>
-      <c r="T37" s="481" t="n"/>
-      <c r="U37" s="482" t="n"/>
-      <c r="V37" s="515" t="n"/>
-      <c r="W37" s="481" t="n"/>
-      <c r="X37" s="481" t="n"/>
-      <c r="Y37" s="481" t="n"/>
-      <c r="Z37" s="481" t="n"/>
-      <c r="AA37" s="481" t="n"/>
-      <c r="AB37" s="481" t="n"/>
-      <c r="AC37" s="481" t="n"/>
-      <c r="AD37" s="481" t="n"/>
-      <c r="AE37" s="482" t="n"/>
-      <c r="AF37" s="511" t="n"/>
-      <c r="AG37" s="481" t="n"/>
-      <c r="AH37" s="481" t="n"/>
-      <c r="AI37" s="482" t="n"/>
-      <c r="AJ37" s="512" t="n"/>
-      <c r="AK37" s="481" t="n"/>
-      <c r="AL37" s="481" t="n"/>
-      <c r="AM37" s="481" t="n"/>
-      <c r="AN37" s="486" t="n"/>
+    <row r="37" ht="17" customHeight="1" s="264">
+      <c r="A37" s="470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5.  REWORK RESULT &amp; DISPOSITION</t>
+        </is>
+      </c>
+      <c r="B37" s="471" t="n"/>
+      <c r="C37" s="471" t="n"/>
+      <c r="D37" s="471" t="n"/>
+      <c r="E37" s="471" t="n"/>
+      <c r="F37" s="471" t="n"/>
+      <c r="G37" s="471" t="n"/>
+      <c r="H37" s="471" t="n"/>
+      <c r="I37" s="471" t="n"/>
+      <c r="J37" s="471" t="n"/>
+      <c r="K37" s="471" t="n"/>
+      <c r="L37" s="471" t="n"/>
+      <c r="M37" s="471" t="n"/>
+      <c r="N37" s="471" t="n"/>
+      <c r="O37" s="471" t="n"/>
+      <c r="P37" s="471" t="n"/>
+      <c r="Q37" s="471" t="n"/>
+      <c r="R37" s="471" t="n"/>
+      <c r="S37" s="471" t="n"/>
+      <c r="T37" s="471" t="n"/>
+      <c r="U37" s="471" t="n"/>
+      <c r="V37" s="471" t="n"/>
+      <c r="W37" s="471" t="n"/>
+      <c r="X37" s="471" t="n"/>
+      <c r="Y37" s="471" t="n"/>
+      <c r="Z37" s="471" t="n"/>
+      <c r="AA37" s="471" t="n"/>
+      <c r="AB37" s="471" t="n"/>
+      <c r="AC37" s="471" t="n"/>
+      <c r="AD37" s="471" t="n"/>
+      <c r="AE37" s="471" t="n"/>
+      <c r="AF37" s="471" t="n"/>
+      <c r="AG37" s="471" t="n"/>
+      <c r="AH37" s="471" t="n"/>
+      <c r="AI37" s="471" t="n"/>
+      <c r="AJ37" s="471" t="n"/>
+      <c r="AK37" s="471" t="n"/>
+      <c r="AL37" s="471" t="n"/>
+      <c r="AM37" s="471" t="n"/>
+      <c r="AN37" s="472" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1" s="264">
-      <c r="A38" s="517">
-        <f>ROW()-ROW($A$30)+1</f>
-        <v/>
-      </c>
-      <c r="B38" s="489" t="n"/>
-      <c r="C38" s="518" t="n"/>
-      <c r="D38" s="488" t="n"/>
-      <c r="E38" s="489" t="n"/>
-      <c r="F38" s="519" t="n"/>
-      <c r="G38" s="488" t="n"/>
-      <c r="H38" s="488" t="n"/>
-      <c r="I38" s="488" t="n"/>
-      <c r="J38" s="488" t="n"/>
-      <c r="K38" s="488" t="n"/>
-      <c r="L38" s="488" t="n"/>
-      <c r="M38" s="488" t="n"/>
-      <c r="N38" s="488" t="n"/>
-      <c r="O38" s="488" t="n"/>
-      <c r="P38" s="488" t="n"/>
-      <c r="Q38" s="488" t="n"/>
-      <c r="R38" s="488" t="n"/>
-      <c r="S38" s="488" t="n"/>
-      <c r="T38" s="488" t="n"/>
-      <c r="U38" s="489" t="n"/>
-      <c r="V38" s="518" t="n"/>
-      <c r="W38" s="488" t="n"/>
-      <c r="X38" s="488" t="n"/>
-      <c r="Y38" s="488" t="n"/>
-      <c r="Z38" s="488" t="n"/>
-      <c r="AA38" s="488" t="n"/>
-      <c r="AB38" s="488" t="n"/>
-      <c r="AC38" s="488" t="n"/>
-      <c r="AD38" s="488" t="n"/>
-      <c r="AE38" s="489" t="n"/>
-      <c r="AF38" s="520" t="n"/>
-      <c r="AG38" s="488" t="n"/>
-      <c r="AH38" s="488" t="n"/>
-      <c r="AI38" s="489" t="n"/>
-      <c r="AJ38" s="521" t="n"/>
-      <c r="AK38" s="488" t="n"/>
-      <c r="AL38" s="488" t="n"/>
-      <c r="AM38" s="488" t="n"/>
-      <c r="AN38" s="493" t="n"/>
+      <c r="A38" s="473" t="inlineStr">
+        <is>
+          <t>Rework Result (Accepted / Scrap / Re-NCR)</t>
+        </is>
+      </c>
+      <c r="B38" s="474" t="n"/>
+      <c r="C38" s="474" t="n"/>
+      <c r="D38" s="474" t="n"/>
+      <c r="E38" s="474" t="n"/>
+      <c r="F38" s="474" t="n"/>
+      <c r="G38" s="475" t="n"/>
+      <c r="H38" s="476" t="n"/>
+      <c r="I38" s="474" t="n"/>
+      <c r="J38" s="474" t="n"/>
+      <c r="K38" s="474" t="n"/>
+      <c r="L38" s="474" t="n"/>
+      <c r="M38" s="474" t="n"/>
+      <c r="N38" s="474" t="n"/>
+      <c r="O38" s="474" t="n"/>
+      <c r="P38" s="474" t="n"/>
+      <c r="Q38" s="474" t="n"/>
+      <c r="R38" s="474" t="n"/>
+      <c r="S38" s="474" t="n"/>
+      <c r="T38" s="475" t="n"/>
+      <c r="U38" s="477" t="inlineStr">
+        <is>
+          <t>Qty Accepted / Scrapped</t>
+        </is>
+      </c>
+      <c r="V38" s="474" t="n"/>
+      <c r="W38" s="474" t="n"/>
+      <c r="X38" s="474" t="n"/>
+      <c r="Y38" s="474" t="n"/>
+      <c r="Z38" s="474" t="n"/>
+      <c r="AA38" s="475" t="n"/>
+      <c r="AB38" s="478" t="n"/>
+      <c r="AC38" s="474" t="n"/>
+      <c r="AD38" s="474" t="n"/>
+      <c r="AE38" s="474" t="n"/>
+      <c r="AF38" s="474" t="n"/>
+      <c r="AG38" s="474" t="n"/>
+      <c r="AH38" s="474" t="n"/>
+      <c r="AI38" s="474" t="n"/>
+      <c r="AJ38" s="474" t="n"/>
+      <c r="AK38" s="474" t="n"/>
+      <c r="AL38" s="474" t="n"/>
+      <c r="AM38" s="474" t="n"/>
+      <c r="AN38" s="479" t="n"/>
     </row>
-    <row r="39" ht="4" customHeight="1" s="264">
-      <c r="A39" s="530" t="n"/>
-      <c r="B39" s="26" t="n"/>
-      <c r="C39" s="26" t="n"/>
-      <c r="D39" s="26" t="n"/>
-      <c r="E39" s="26" t="n"/>
-      <c r="F39" s="26" t="n"/>
-      <c r="G39" s="26" t="n"/>
-      <c r="H39" s="26" t="n"/>
-      <c r="I39" s="26" t="n"/>
-      <c r="J39" s="26" t="n"/>
-      <c r="K39" s="26" t="n"/>
-      <c r="L39" s="26" t="n"/>
-      <c r="M39" s="26" t="n"/>
-      <c r="N39" s="26" t="n"/>
-      <c r="O39" s="26" t="n"/>
-      <c r="P39" s="26" t="n"/>
-      <c r="Q39" s="26" t="n"/>
-      <c r="R39" s="26" t="n"/>
-      <c r="S39" s="26" t="n"/>
-      <c r="T39" s="26" t="n"/>
-      <c r="U39" s="26" t="n"/>
-      <c r="V39" s="26" t="n"/>
-      <c r="W39" s="26" t="n"/>
-      <c r="X39" s="26" t="n"/>
-      <c r="Y39" s="26" t="n"/>
-      <c r="Z39" s="26" t="n"/>
-      <c r="AA39" s="26" t="n"/>
-      <c r="AB39" s="26" t="n"/>
-      <c r="AC39" s="26" t="n"/>
-      <c r="AD39" s="26" t="n"/>
-      <c r="AE39" s="26" t="n"/>
-      <c r="AF39" s="26" t="n"/>
-      <c r="AG39" s="26" t="n"/>
-      <c r="AH39" s="26" t="n"/>
-      <c r="AI39" s="26" t="n"/>
-      <c r="AJ39" s="26" t="n"/>
-      <c r="AK39" s="26" t="n"/>
-      <c r="AL39" s="26" t="n"/>
-      <c r="AM39" s="26" t="n"/>
-      <c r="AN39" s="26" t="n"/>
+    <row r="39" ht="20" customHeight="1" s="264">
+      <c r="A39" s="487" t="inlineStr">
+        <is>
+          <t>New Tray Status (WI-703)</t>
+        </is>
+      </c>
+      <c r="B39" s="488" t="n"/>
+      <c r="C39" s="488" t="n"/>
+      <c r="D39" s="488" t="n"/>
+      <c r="E39" s="488" t="n"/>
+      <c r="F39" s="488" t="n"/>
+      <c r="G39" s="489" t="n"/>
+      <c r="H39" s="490" t="n"/>
+      <c r="I39" s="488" t="n"/>
+      <c r="J39" s="488" t="n"/>
+      <c r="K39" s="488" t="n"/>
+      <c r="L39" s="488" t="n"/>
+      <c r="M39" s="488" t="n"/>
+      <c r="N39" s="488" t="n"/>
+      <c r="O39" s="488" t="n"/>
+      <c r="P39" s="488" t="n"/>
+      <c r="Q39" s="488" t="n"/>
+      <c r="R39" s="488" t="n"/>
+      <c r="S39" s="488" t="n"/>
+      <c r="T39" s="489" t="n"/>
+      <c r="U39" s="491" t="inlineStr">
+        <is>
+          <t>Concession Permit Ref (FRM-656)</t>
+        </is>
+      </c>
+      <c r="V39" s="488" t="n"/>
+      <c r="W39" s="488" t="n"/>
+      <c r="X39" s="488" t="n"/>
+      <c r="Y39" s="488" t="n"/>
+      <c r="Z39" s="488" t="n"/>
+      <c r="AA39" s="489" t="n"/>
+      <c r="AB39" s="492" t="n"/>
+      <c r="AC39" s="488" t="n"/>
+      <c r="AD39" s="488" t="n"/>
+      <c r="AE39" s="488" t="n"/>
+      <c r="AF39" s="488" t="n"/>
+      <c r="AG39" s="488" t="n"/>
+      <c r="AH39" s="488" t="n"/>
+      <c r="AI39" s="488" t="n"/>
+      <c r="AJ39" s="488" t="n"/>
+      <c r="AK39" s="488" t="n"/>
+      <c r="AL39" s="488" t="n"/>
+      <c r="AM39" s="488" t="n"/>
+      <c r="AN39" s="493" t="n"/>
     </row>
-    <row r="40" ht="17" customHeight="1" s="264">
-      <c r="A40" s="470" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5.  REWORK RESULT &amp; DISPOSITION</t>
-        </is>
-      </c>
-      <c r="B40" s="471" t="n"/>
-      <c r="C40" s="471" t="n"/>
-      <c r="D40" s="471" t="n"/>
-      <c r="E40" s="471" t="n"/>
-      <c r="F40" s="471" t="n"/>
-      <c r="G40" s="471" t="n"/>
-      <c r="H40" s="471" t="n"/>
-      <c r="I40" s="471" t="n"/>
-      <c r="J40" s="471" t="n"/>
-      <c r="K40" s="471" t="n"/>
-      <c r="L40" s="471" t="n"/>
-      <c r="M40" s="471" t="n"/>
-      <c r="N40" s="471" t="n"/>
-      <c r="O40" s="471" t="n"/>
-      <c r="P40" s="471" t="n"/>
-      <c r="Q40" s="471" t="n"/>
-      <c r="R40" s="471" t="n"/>
-      <c r="S40" s="471" t="n"/>
-      <c r="T40" s="471" t="n"/>
-      <c r="U40" s="471" t="n"/>
-      <c r="V40" s="471" t="n"/>
-      <c r="W40" s="471" t="n"/>
-      <c r="X40" s="471" t="n"/>
-      <c r="Y40" s="471" t="n"/>
-      <c r="Z40" s="471" t="n"/>
-      <c r="AA40" s="471" t="n"/>
-      <c r="AB40" s="471" t="n"/>
-      <c r="AC40" s="471" t="n"/>
-      <c r="AD40" s="471" t="n"/>
-      <c r="AE40" s="471" t="n"/>
-      <c r="AF40" s="471" t="n"/>
-      <c r="AG40" s="471" t="n"/>
-      <c r="AH40" s="471" t="n"/>
-      <c r="AI40" s="471" t="n"/>
-      <c r="AJ40" s="471" t="n"/>
-      <c r="AK40" s="471" t="n"/>
-      <c r="AL40" s="471" t="n"/>
-      <c r="AM40" s="471" t="n"/>
-      <c r="AN40" s="472" t="n"/>
+    <row r="40" ht="4" customHeight="1" s="264">
+      <c r="A40" s="523" t="n"/>
+      <c r="B40" s="26" t="n"/>
+      <c r="C40" s="26" t="n"/>
+      <c r="D40" s="26" t="n"/>
+      <c r="E40" s="26" t="n"/>
+      <c r="F40" s="26" t="n"/>
+      <c r="G40" s="26" t="n"/>
+      <c r="H40" s="26" t="n"/>
+      <c r="I40" s="26" t="n"/>
+      <c r="J40" s="26" t="n"/>
+      <c r="K40" s="26" t="n"/>
+      <c r="L40" s="26" t="n"/>
+      <c r="M40" s="26" t="n"/>
+      <c r="N40" s="26" t="n"/>
+      <c r="O40" s="26" t="n"/>
+      <c r="P40" s="26" t="n"/>
+      <c r="Q40" s="26" t="n"/>
+      <c r="R40" s="26" t="n"/>
+      <c r="S40" s="26" t="n"/>
+      <c r="T40" s="26" t="n"/>
+      <c r="U40" s="26" t="n"/>
+      <c r="V40" s="26" t="n"/>
+      <c r="W40" s="26" t="n"/>
+      <c r="X40" s="26" t="n"/>
+      <c r="Y40" s="26" t="n"/>
+      <c r="Z40" s="26" t="n"/>
+      <c r="AA40" s="26" t="n"/>
+      <c r="AB40" s="26" t="n"/>
+      <c r="AC40" s="26" t="n"/>
+      <c r="AD40" s="26" t="n"/>
+      <c r="AE40" s="26" t="n"/>
+      <c r="AF40" s="26" t="n"/>
+      <c r="AG40" s="26" t="n"/>
+      <c r="AH40" s="26" t="n"/>
+      <c r="AI40" s="26" t="n"/>
+      <c r="AJ40" s="26" t="n"/>
+      <c r="AK40" s="26" t="n"/>
+      <c r="AL40" s="26" t="n"/>
+      <c r="AM40" s="26" t="n"/>
+      <c r="AN40" s="26" t="n"/>
     </row>
-    <row r="41" ht="20" customHeight="1" s="264">
-      <c r="A41" s="473" t="inlineStr">
-        <is>
-          <t>Rework Result (Accepted / Scrap / Re-NCR)</t>
-        </is>
-      </c>
-      <c r="B41" s="474" t="n"/>
-      <c r="C41" s="474" t="n"/>
-      <c r="D41" s="474" t="n"/>
-      <c r="E41" s="474" t="n"/>
-      <c r="F41" s="474" t="n"/>
-      <c r="G41" s="475" t="n"/>
-      <c r="H41" s="476" t="n"/>
-      <c r="I41" s="474" t="n"/>
-      <c r="J41" s="474" t="n"/>
-      <c r="K41" s="474" t="n"/>
-      <c r="L41" s="474" t="n"/>
-      <c r="M41" s="474" t="n"/>
-      <c r="N41" s="474" t="n"/>
-      <c r="O41" s="474" t="n"/>
-      <c r="P41" s="474" t="n"/>
-      <c r="Q41" s="474" t="n"/>
-      <c r="R41" s="474" t="n"/>
-      <c r="S41" s="474" t="n"/>
-      <c r="T41" s="475" t="n"/>
-      <c r="U41" s="477" t="inlineStr">
-        <is>
-          <t>Qty Accepted / Scrapped</t>
-        </is>
-      </c>
-      <c r="V41" s="474" t="n"/>
-      <c r="W41" s="474" t="n"/>
-      <c r="X41" s="474" t="n"/>
-      <c r="Y41" s="474" t="n"/>
-      <c r="Z41" s="474" t="n"/>
-      <c r="AA41" s="475" t="n"/>
-      <c r="AB41" s="478" t="n"/>
-      <c r="AC41" s="474" t="n"/>
-      <c r="AD41" s="474" t="n"/>
-      <c r="AE41" s="474" t="n"/>
-      <c r="AF41" s="474" t="n"/>
-      <c r="AG41" s="474" t="n"/>
-      <c r="AH41" s="474" t="n"/>
-      <c r="AI41" s="474" t="n"/>
-      <c r="AJ41" s="474" t="n"/>
-      <c r="AK41" s="474" t="n"/>
-      <c r="AL41" s="474" t="n"/>
-      <c r="AM41" s="474" t="n"/>
-      <c r="AN41" s="479" t="n"/>
+    <row r="41" ht="17" customHeight="1" s="264">
+      <c r="A41" s="470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6.  APPROVAL</t>
+        </is>
+      </c>
+      <c r="B41" s="471" t="n"/>
+      <c r="C41" s="471" t="n"/>
+      <c r="D41" s="471" t="n"/>
+      <c r="E41" s="471" t="n"/>
+      <c r="F41" s="471" t="n"/>
+      <c r="G41" s="471" t="n"/>
+      <c r="H41" s="471" t="n"/>
+      <c r="I41" s="471" t="n"/>
+      <c r="J41" s="471" t="n"/>
+      <c r="K41" s="471" t="n"/>
+      <c r="L41" s="471" t="n"/>
+      <c r="M41" s="471" t="n"/>
+      <c r="N41" s="471" t="n"/>
+      <c r="O41" s="471" t="n"/>
+      <c r="P41" s="471" t="n"/>
+      <c r="Q41" s="471" t="n"/>
+      <c r="R41" s="471" t="n"/>
+      <c r="S41" s="471" t="n"/>
+      <c r="T41" s="471" t="n"/>
+      <c r="U41" s="471" t="n"/>
+      <c r="V41" s="471" t="n"/>
+      <c r="W41" s="471" t="n"/>
+      <c r="X41" s="471" t="n"/>
+      <c r="Y41" s="471" t="n"/>
+      <c r="Z41" s="471" t="n"/>
+      <c r="AA41" s="471" t="n"/>
+      <c r="AB41" s="471" t="n"/>
+      <c r="AC41" s="471" t="n"/>
+      <c r="AD41" s="471" t="n"/>
+      <c r="AE41" s="471" t="n"/>
+      <c r="AF41" s="471" t="n"/>
+      <c r="AG41" s="471" t="n"/>
+      <c r="AH41" s="471" t="n"/>
+      <c r="AI41" s="471" t="n"/>
+      <c r="AJ41" s="471" t="n"/>
+      <c r="AK41" s="471" t="n"/>
+      <c r="AL41" s="471" t="n"/>
+      <c r="AM41" s="471" t="n"/>
+      <c r="AN41" s="472" t="n"/>
     </row>
-    <row r="42" ht="20" customHeight="1" s="264">
-      <c r="A42" s="487" t="inlineStr">
-        <is>
-          <t>New Tray Status (WI-703)</t>
-        </is>
-      </c>
-      <c r="B42" s="488" t="n"/>
-      <c r="C42" s="488" t="n"/>
-      <c r="D42" s="488" t="n"/>
-      <c r="E42" s="488" t="n"/>
-      <c r="F42" s="488" t="n"/>
-      <c r="G42" s="489" t="n"/>
-      <c r="H42" s="490" t="n"/>
-      <c r="I42" s="488" t="n"/>
-      <c r="J42" s="488" t="n"/>
-      <c r="K42" s="488" t="n"/>
-      <c r="L42" s="488" t="n"/>
-      <c r="M42" s="488" t="n"/>
-      <c r="N42" s="488" t="n"/>
-      <c r="O42" s="488" t="n"/>
-      <c r="P42" s="488" t="n"/>
-      <c r="Q42" s="488" t="n"/>
-      <c r="R42" s="488" t="n"/>
-      <c r="S42" s="488" t="n"/>
-      <c r="T42" s="489" t="n"/>
-      <c r="U42" s="491" t="inlineStr">
-        <is>
-          <t>Concession Permit Ref (FRM-656)</t>
-        </is>
-      </c>
-      <c r="V42" s="488" t="n"/>
-      <c r="W42" s="488" t="n"/>
-      <c r="X42" s="488" t="n"/>
-      <c r="Y42" s="488" t="n"/>
-      <c r="Z42" s="488" t="n"/>
-      <c r="AA42" s="489" t="n"/>
-      <c r="AB42" s="492" t="n"/>
-      <c r="AC42" s="488" t="n"/>
-      <c r="AD42" s="488" t="n"/>
-      <c r="AE42" s="488" t="n"/>
-      <c r="AF42" s="488" t="n"/>
-      <c r="AG42" s="488" t="n"/>
-      <c r="AH42" s="488" t="n"/>
-      <c r="AI42" s="488" t="n"/>
-      <c r="AJ42" s="488" t="n"/>
-      <c r="AK42" s="488" t="n"/>
-      <c r="AL42" s="488" t="n"/>
-      <c r="AM42" s="488" t="n"/>
-      <c r="AN42" s="493" t="n"/>
+    <row r="42" ht="17" customHeight="1" s="264">
+      <c r="A42" s="515" t="inlineStr">
+        <is>
+          <t>Rework Operator</t>
+        </is>
+      </c>
+      <c r="B42" s="471" t="n"/>
+      <c r="C42" s="471" t="n"/>
+      <c r="D42" s="471" t="n"/>
+      <c r="E42" s="471" t="n"/>
+      <c r="F42" s="471" t="n"/>
+      <c r="G42" s="471" t="n"/>
+      <c r="H42" s="471" t="n"/>
+      <c r="I42" s="471" t="n"/>
+      <c r="J42" s="471" t="n"/>
+      <c r="K42" s="471" t="n"/>
+      <c r="L42" s="471" t="n"/>
+      <c r="M42" s="472" t="n"/>
+      <c r="N42" s="515" t="inlineStr">
+        <is>
+          <t>QC Verifier</t>
+        </is>
+      </c>
+      <c r="O42" s="471" t="n"/>
+      <c r="P42" s="471" t="n"/>
+      <c r="Q42" s="471" t="n"/>
+      <c r="R42" s="471" t="n"/>
+      <c r="S42" s="471" t="n"/>
+      <c r="T42" s="471" t="n"/>
+      <c r="U42" s="471" t="n"/>
+      <c r="V42" s="471" t="n"/>
+      <c r="W42" s="471" t="n"/>
+      <c r="X42" s="471" t="n"/>
+      <c r="Y42" s="471" t="n"/>
+      <c r="Z42" s="472" t="n"/>
+      <c r="AA42" s="515" t="inlineStr">
+        <is>
+          <t>QA Manager</t>
+        </is>
+      </c>
+      <c r="AB42" s="471" t="n"/>
+      <c r="AC42" s="471" t="n"/>
+      <c r="AD42" s="471" t="n"/>
+      <c r="AE42" s="471" t="n"/>
+      <c r="AF42" s="471" t="n"/>
+      <c r="AG42" s="471" t="n"/>
+      <c r="AH42" s="471" t="n"/>
+      <c r="AI42" s="471" t="n"/>
+      <c r="AJ42" s="471" t="n"/>
+      <c r="AK42" s="471" t="n"/>
+      <c r="AL42" s="471" t="n"/>
+      <c r="AM42" s="471" t="n"/>
+      <c r="AN42" s="472" t="n"/>
     </row>
-    <row r="43" ht="4" customHeight="1" s="264">
-      <c r="A43" s="530" t="n"/>
-      <c r="B43" s="26" t="n"/>
-      <c r="C43" s="26" t="n"/>
-      <c r="D43" s="26" t="n"/>
-      <c r="E43" s="26" t="n"/>
-      <c r="F43" s="26" t="n"/>
-      <c r="G43" s="26" t="n"/>
-      <c r="H43" s="26" t="n"/>
-      <c r="I43" s="26" t="n"/>
-      <c r="J43" s="26" t="n"/>
-      <c r="K43" s="26" t="n"/>
-      <c r="L43" s="26" t="n"/>
-      <c r="M43" s="26" t="n"/>
-      <c r="N43" s="26" t="n"/>
-      <c r="O43" s="26" t="n"/>
-      <c r="P43" s="26" t="n"/>
-      <c r="Q43" s="26" t="n"/>
-      <c r="R43" s="26" t="n"/>
-      <c r="S43" s="26" t="n"/>
-      <c r="T43" s="26" t="n"/>
-      <c r="U43" s="26" t="n"/>
-      <c r="V43" s="26" t="n"/>
-      <c r="W43" s="26" t="n"/>
-      <c r="X43" s="26" t="n"/>
-      <c r="Y43" s="26" t="n"/>
-      <c r="Z43" s="26" t="n"/>
-      <c r="AA43" s="26" t="n"/>
-      <c r="AB43" s="26" t="n"/>
-      <c r="AC43" s="26" t="n"/>
-      <c r="AD43" s="26" t="n"/>
-      <c r="AE43" s="26" t="n"/>
-      <c r="AF43" s="26" t="n"/>
-      <c r="AG43" s="26" t="n"/>
-      <c r="AH43" s="26" t="n"/>
-      <c r="AI43" s="26" t="n"/>
-      <c r="AJ43" s="26" t="n"/>
-      <c r="AK43" s="26" t="n"/>
-      <c r="AL43" s="26" t="n"/>
-      <c r="AM43" s="26" t="n"/>
-      <c r="AN43" s="26" t="n"/>
+    <row r="43" ht="26" customHeight="1" s="264">
+      <c r="A43" s="516" t="inlineStr">
+        <is>
+          <t>Name  /  Signature  /  Date</t>
+        </is>
+      </c>
+      <c r="B43" s="517" t="n"/>
+      <c r="C43" s="517" t="n"/>
+      <c r="D43" s="517" t="n"/>
+      <c r="E43" s="517" t="n"/>
+      <c r="F43" s="517" t="n"/>
+      <c r="G43" s="517" t="n"/>
+      <c r="H43" s="517" t="n"/>
+      <c r="I43" s="517" t="n"/>
+      <c r="J43" s="517" t="n"/>
+      <c r="K43" s="517" t="n"/>
+      <c r="L43" s="517" t="n"/>
+      <c r="M43" s="518" t="n"/>
+      <c r="N43" s="516" t="inlineStr">
+        <is>
+          <t>Name  /  Signature  /  Date</t>
+        </is>
+      </c>
+      <c r="O43" s="517" t="n"/>
+      <c r="P43" s="517" t="n"/>
+      <c r="Q43" s="517" t="n"/>
+      <c r="R43" s="517" t="n"/>
+      <c r="S43" s="517" t="n"/>
+      <c r="T43" s="517" t="n"/>
+      <c r="U43" s="517" t="n"/>
+      <c r="V43" s="517" t="n"/>
+      <c r="W43" s="517" t="n"/>
+      <c r="X43" s="517" t="n"/>
+      <c r="Y43" s="517" t="n"/>
+      <c r="Z43" s="518" t="n"/>
+      <c r="AA43" s="516" t="inlineStr">
+        <is>
+          <t>Name  /  Signature  /  Date</t>
+        </is>
+      </c>
+      <c r="AB43" s="517" t="n"/>
+      <c r="AC43" s="517" t="n"/>
+      <c r="AD43" s="517" t="n"/>
+      <c r="AE43" s="517" t="n"/>
+      <c r="AF43" s="517" t="n"/>
+      <c r="AG43" s="517" t="n"/>
+      <c r="AH43" s="517" t="n"/>
+      <c r="AI43" s="517" t="n"/>
+      <c r="AJ43" s="517" t="n"/>
+      <c r="AK43" s="517" t="n"/>
+      <c r="AL43" s="517" t="n"/>
+      <c r="AM43" s="517" t="n"/>
+      <c r="AN43" s="518" t="n"/>
     </row>
-    <row r="44" ht="17" customHeight="1" s="264">
-      <c r="A44" s="470" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  6.  APPROVAL</t>
-        </is>
-      </c>
-      <c r="B44" s="471" t="n"/>
-      <c r="C44" s="471" t="n"/>
-      <c r="D44" s="471" t="n"/>
-      <c r="E44" s="471" t="n"/>
-      <c r="F44" s="471" t="n"/>
-      <c r="G44" s="471" t="n"/>
-      <c r="H44" s="471" t="n"/>
-      <c r="I44" s="471" t="n"/>
-      <c r="J44" s="471" t="n"/>
-      <c r="K44" s="471" t="n"/>
-      <c r="L44" s="471" t="n"/>
-      <c r="M44" s="471" t="n"/>
-      <c r="N44" s="471" t="n"/>
-      <c r="O44" s="471" t="n"/>
-      <c r="P44" s="471" t="n"/>
-      <c r="Q44" s="471" t="n"/>
-      <c r="R44" s="471" t="n"/>
-      <c r="S44" s="471" t="n"/>
-      <c r="T44" s="471" t="n"/>
-      <c r="U44" s="471" t="n"/>
-      <c r="V44" s="471" t="n"/>
-      <c r="W44" s="471" t="n"/>
-      <c r="X44" s="471" t="n"/>
-      <c r="Y44" s="471" t="n"/>
-      <c r="Z44" s="471" t="n"/>
-      <c r="AA44" s="471" t="n"/>
-      <c r="AB44" s="471" t="n"/>
-      <c r="AC44" s="471" t="n"/>
-      <c r="AD44" s="471" t="n"/>
-      <c r="AE44" s="471" t="n"/>
-      <c r="AF44" s="471" t="n"/>
-      <c r="AG44" s="471" t="n"/>
-      <c r="AH44" s="471" t="n"/>
-      <c r="AI44" s="471" t="n"/>
-      <c r="AJ44" s="471" t="n"/>
-      <c r="AK44" s="471" t="n"/>
-      <c r="AL44" s="471" t="n"/>
-      <c r="AM44" s="471" t="n"/>
-      <c r="AN44" s="472" t="n"/>
+    <row r="44" ht="26" customHeight="1" s="264">
+      <c r="A44" s="519" t="n"/>
+      <c r="M44" s="520" t="n"/>
+      <c r="N44" s="519" t="n"/>
+      <c r="Z44" s="520" t="n"/>
+      <c r="AA44" s="519" t="n"/>
+      <c r="AN44" s="520" t="n"/>
     </row>
-    <row r="45" ht="17" customHeight="1" s="264">
-      <c r="A45" s="522" t="inlineStr">
-        <is>
-          <t>Rework Operator</t>
-        </is>
-      </c>
-      <c r="B45" s="471" t="n"/>
-      <c r="C45" s="471" t="n"/>
-      <c r="D45" s="471" t="n"/>
-      <c r="E45" s="471" t="n"/>
-      <c r="F45" s="471" t="n"/>
-      <c r="G45" s="471" t="n"/>
-      <c r="H45" s="471" t="n"/>
-      <c r="I45" s="471" t="n"/>
-      <c r="J45" s="471" t="n"/>
-      <c r="K45" s="471" t="n"/>
-      <c r="L45" s="471" t="n"/>
-      <c r="M45" s="472" t="n"/>
-      <c r="N45" s="522" t="inlineStr">
-        <is>
-          <t>QC Verifier</t>
-        </is>
-      </c>
-      <c r="O45" s="471" t="n"/>
-      <c r="P45" s="471" t="n"/>
-      <c r="Q45" s="471" t="n"/>
-      <c r="R45" s="471" t="n"/>
-      <c r="S45" s="471" t="n"/>
-      <c r="T45" s="471" t="n"/>
-      <c r="U45" s="471" t="n"/>
-      <c r="V45" s="471" t="n"/>
-      <c r="W45" s="471" t="n"/>
-      <c r="X45" s="471" t="n"/>
-      <c r="Y45" s="471" t="n"/>
-      <c r="Z45" s="472" t="n"/>
-      <c r="AA45" s="522" t="inlineStr">
-        <is>
-          <t>QA Manager</t>
-        </is>
-      </c>
-      <c r="AB45" s="471" t="n"/>
-      <c r="AC45" s="471" t="n"/>
-      <c r="AD45" s="471" t="n"/>
-      <c r="AE45" s="471" t="n"/>
-      <c r="AF45" s="471" t="n"/>
-      <c r="AG45" s="471" t="n"/>
-      <c r="AH45" s="471" t="n"/>
-      <c r="AI45" s="471" t="n"/>
-      <c r="AJ45" s="471" t="n"/>
-      <c r="AK45" s="471" t="n"/>
-      <c r="AL45" s="471" t="n"/>
-      <c r="AM45" s="471" t="n"/>
-      <c r="AN45" s="472" t="n"/>
+    <row r="45" ht="26" customHeight="1" s="264">
+      <c r="A45" s="521" t="n"/>
+      <c r="B45" s="488" t="n"/>
+      <c r="C45" s="488" t="n"/>
+      <c r="D45" s="488" t="n"/>
+      <c r="E45" s="488" t="n"/>
+      <c r="F45" s="488" t="n"/>
+      <c r="G45" s="488" t="n"/>
+      <c r="H45" s="488" t="n"/>
+      <c r="I45" s="488" t="n"/>
+      <c r="J45" s="488" t="n"/>
+      <c r="K45" s="488" t="n"/>
+      <c r="L45" s="488" t="n"/>
+      <c r="M45" s="493" t="n"/>
+      <c r="N45" s="521" t="n"/>
+      <c r="O45" s="488" t="n"/>
+      <c r="P45" s="488" t="n"/>
+      <c r="Q45" s="488" t="n"/>
+      <c r="R45" s="488" t="n"/>
+      <c r="S45" s="488" t="n"/>
+      <c r="T45" s="488" t="n"/>
+      <c r="U45" s="488" t="n"/>
+      <c r="V45" s="488" t="n"/>
+      <c r="W45" s="488" t="n"/>
+      <c r="X45" s="488" t="n"/>
+      <c r="Y45" s="488" t="n"/>
+      <c r="Z45" s="493" t="n"/>
+      <c r="AA45" s="521" t="n"/>
+      <c r="AB45" s="488" t="n"/>
+      <c r="AC45" s="488" t="n"/>
+      <c r="AD45" s="488" t="n"/>
+      <c r="AE45" s="488" t="n"/>
+      <c r="AF45" s="488" t="n"/>
+      <c r="AG45" s="488" t="n"/>
+      <c r="AH45" s="488" t="n"/>
+      <c r="AI45" s="488" t="n"/>
+      <c r="AJ45" s="488" t="n"/>
+      <c r="AK45" s="488" t="n"/>
+      <c r="AL45" s="488" t="n"/>
+      <c r="AM45" s="488" t="n"/>
+      <c r="AN45" s="493" t="n"/>
     </row>
-    <row r="46" ht="26" customHeight="1" s="264">
-      <c r="A46" s="523" t="inlineStr">
-        <is>
-          <t>Name  /  Signature  /  Date</t>
-        </is>
-      </c>
-      <c r="B46" s="524" t="n"/>
-      <c r="C46" s="524" t="n"/>
-      <c r="D46" s="524" t="n"/>
-      <c r="E46" s="524" t="n"/>
-      <c r="F46" s="524" t="n"/>
-      <c r="G46" s="524" t="n"/>
-      <c r="H46" s="524" t="n"/>
-      <c r="I46" s="524" t="n"/>
-      <c r="J46" s="524" t="n"/>
-      <c r="K46" s="524" t="n"/>
-      <c r="L46" s="524" t="n"/>
-      <c r="M46" s="525" t="n"/>
-      <c r="N46" s="523" t="inlineStr">
-        <is>
-          <t>Name  /  Signature  /  Date</t>
-        </is>
-      </c>
-      <c r="O46" s="524" t="n"/>
-      <c r="P46" s="524" t="n"/>
-      <c r="Q46" s="524" t="n"/>
-      <c r="R46" s="524" t="n"/>
-      <c r="S46" s="524" t="n"/>
-      <c r="T46" s="524" t="n"/>
-      <c r="U46" s="524" t="n"/>
-      <c r="V46" s="524" t="n"/>
-      <c r="W46" s="524" t="n"/>
-      <c r="X46" s="524" t="n"/>
-      <c r="Y46" s="524" t="n"/>
-      <c r="Z46" s="525" t="n"/>
-      <c r="AA46" s="523" t="inlineStr">
-        <is>
-          <t>Name  /  Signature  /  Date</t>
-        </is>
-      </c>
-      <c r="AB46" s="524" t="n"/>
-      <c r="AC46" s="524" t="n"/>
-      <c r="AD46" s="524" t="n"/>
-      <c r="AE46" s="524" t="n"/>
-      <c r="AF46" s="524" t="n"/>
-      <c r="AG46" s="524" t="n"/>
-      <c r="AH46" s="524" t="n"/>
-      <c r="AI46" s="524" t="n"/>
-      <c r="AJ46" s="524" t="n"/>
-      <c r="AK46" s="524" t="n"/>
-      <c r="AL46" s="524" t="n"/>
-      <c r="AM46" s="524" t="n"/>
-      <c r="AN46" s="525" t="n"/>
+    <row r="46" ht="4" customHeight="1" s="264">
+      <c r="A46" s="523" t="n"/>
+      <c r="B46" s="26" t="n"/>
+      <c r="C46" s="26" t="n"/>
+      <c r="D46" s="26" t="n"/>
+      <c r="E46" s="26" t="n"/>
+      <c r="F46" s="26" t="n"/>
+      <c r="G46" s="26" t="n"/>
+      <c r="H46" s="26" t="n"/>
+      <c r="I46" s="26" t="n"/>
+      <c r="J46" s="26" t="n"/>
+      <c r="K46" s="26" t="n"/>
+      <c r="L46" s="26" t="n"/>
+      <c r="M46" s="26" t="n"/>
+      <c r="N46" s="26" t="n"/>
+      <c r="O46" s="26" t="n"/>
+      <c r="P46" s="26" t="n"/>
+      <c r="Q46" s="26" t="n"/>
+      <c r="R46" s="26" t="n"/>
+      <c r="S46" s="26" t="n"/>
+      <c r="T46" s="26" t="n"/>
+      <c r="U46" s="26" t="n"/>
+      <c r="V46" s="26" t="n"/>
+      <c r="W46" s="26" t="n"/>
+      <c r="X46" s="26" t="n"/>
+      <c r="Y46" s="26" t="n"/>
+      <c r="Z46" s="26" t="n"/>
+      <c r="AA46" s="26" t="n"/>
+      <c r="AB46" s="26" t="n"/>
+      <c r="AC46" s="26" t="n"/>
+      <c r="AD46" s="26" t="n"/>
+      <c r="AE46" s="26" t="n"/>
+      <c r="AF46" s="26" t="n"/>
+      <c r="AG46" s="26" t="n"/>
+      <c r="AH46" s="26" t="n"/>
+      <c r="AI46" s="26" t="n"/>
+      <c r="AJ46" s="26" t="n"/>
+      <c r="AK46" s="26" t="n"/>
+      <c r="AL46" s="26" t="n"/>
+      <c r="AM46" s="26" t="n"/>
+      <c r="AN46" s="26" t="n"/>
     </row>
-    <row r="47" ht="26" customHeight="1" s="264">
-      <c r="A47" s="526" t="n"/>
-      <c r="M47" s="527" t="n"/>
-      <c r="N47" s="526" t="n"/>
-      <c r="Z47" s="527" t="n"/>
-      <c r="AA47" s="526" t="n"/>
-      <c r="AN47" s="527" t="n"/>
-    </row>
-    <row r="48" ht="26" customHeight="1" s="264">
-      <c r="A48" s="528" t="n"/>
-      <c r="B48" s="488" t="n"/>
-      <c r="C48" s="488" t="n"/>
-      <c r="D48" s="488" t="n"/>
-      <c r="E48" s="488" t="n"/>
-      <c r="F48" s="488" t="n"/>
-      <c r="G48" s="488" t="n"/>
-      <c r="H48" s="488" t="n"/>
-      <c r="I48" s="488" t="n"/>
-      <c r="J48" s="488" t="n"/>
-      <c r="K48" s="488" t="n"/>
-      <c r="L48" s="488" t="n"/>
-      <c r="M48" s="493" t="n"/>
-      <c r="N48" s="528" t="n"/>
-      <c r="O48" s="488" t="n"/>
-      <c r="P48" s="488" t="n"/>
-      <c r="Q48" s="488" t="n"/>
-      <c r="R48" s="488" t="n"/>
-      <c r="S48" s="488" t="n"/>
-      <c r="T48" s="488" t="n"/>
-      <c r="U48" s="488" t="n"/>
-      <c r="V48" s="488" t="n"/>
-      <c r="W48" s="488" t="n"/>
-      <c r="X48" s="488" t="n"/>
-      <c r="Y48" s="488" t="n"/>
-      <c r="Z48" s="493" t="n"/>
-      <c r="AA48" s="528" t="n"/>
-      <c r="AB48" s="488" t="n"/>
-      <c r="AC48" s="488" t="n"/>
-      <c r="AD48" s="488" t="n"/>
-      <c r="AE48" s="488" t="n"/>
-      <c r="AF48" s="488" t="n"/>
-      <c r="AG48" s="488" t="n"/>
-      <c r="AH48" s="488" t="n"/>
-      <c r="AI48" s="488" t="n"/>
-      <c r="AJ48" s="488" t="n"/>
-      <c r="AK48" s="488" t="n"/>
-      <c r="AL48" s="488" t="n"/>
-      <c r="AM48" s="488" t="n"/>
-      <c r="AN48" s="493" t="n"/>
-    </row>
-    <row r="49" ht="4" customHeight="1" s="264">
-      <c r="A49" s="530" t="n"/>
-      <c r="B49" s="26" t="n"/>
-      <c r="C49" s="26" t="n"/>
-      <c r="D49" s="26" t="n"/>
-      <c r="E49" s="26" t="n"/>
-      <c r="F49" s="26" t="n"/>
-      <c r="G49" s="26" t="n"/>
-      <c r="H49" s="26" t="n"/>
-      <c r="I49" s="26" t="n"/>
-      <c r="J49" s="26" t="n"/>
-      <c r="K49" s="26" t="n"/>
-      <c r="L49" s="26" t="n"/>
-      <c r="M49" s="26" t="n"/>
-      <c r="N49" s="26" t="n"/>
-      <c r="O49" s="26" t="n"/>
-      <c r="P49" s="26" t="n"/>
-      <c r="Q49" s="26" t="n"/>
-      <c r="R49" s="26" t="n"/>
-      <c r="S49" s="26" t="n"/>
-      <c r="T49" s="26" t="n"/>
-      <c r="U49" s="26" t="n"/>
-      <c r="V49" s="26" t="n"/>
-      <c r="W49" s="26" t="n"/>
-      <c r="X49" s="26" t="n"/>
-      <c r="Y49" s="26" t="n"/>
-      <c r="Z49" s="26" t="n"/>
-      <c r="AA49" s="26" t="n"/>
-      <c r="AB49" s="26" t="n"/>
-      <c r="AC49" s="26" t="n"/>
-      <c r="AD49" s="26" t="n"/>
-      <c r="AE49" s="26" t="n"/>
-      <c r="AF49" s="26" t="n"/>
-      <c r="AG49" s="26" t="n"/>
-      <c r="AH49" s="26" t="n"/>
-      <c r="AI49" s="26" t="n"/>
-      <c r="AJ49" s="26" t="n"/>
-      <c r="AK49" s="26" t="n"/>
-      <c r="AL49" s="26" t="n"/>
-      <c r="AM49" s="26" t="n"/>
-      <c r="AN49" s="26" t="n"/>
-    </row>
-    <row r="50" ht="24" customHeight="1" s="264">
-      <c r="A50" s="529" t="inlineStr">
-        <is>
-          <t>NOTICE — Rework may only proceed against an approved method. Repair (permanent deviation from drawing) additionally requires a Concession Permit (FRM-656). Ref: SOP-505 / FRM-651. Retain: 10 years.</t>
-        </is>
-      </c>
-      <c r="B50" s="471" t="n"/>
-      <c r="C50" s="471" t="n"/>
-      <c r="D50" s="471" t="n"/>
-      <c r="E50" s="471" t="n"/>
-      <c r="F50" s="471" t="n"/>
-      <c r="G50" s="471" t="n"/>
-      <c r="H50" s="471" t="n"/>
-      <c r="I50" s="471" t="n"/>
-      <c r="J50" s="471" t="n"/>
-      <c r="K50" s="471" t="n"/>
-      <c r="L50" s="471" t="n"/>
-      <c r="M50" s="471" t="n"/>
-      <c r="N50" s="471" t="n"/>
-      <c r="O50" s="471" t="n"/>
-      <c r="P50" s="471" t="n"/>
-      <c r="Q50" s="471" t="n"/>
-      <c r="R50" s="471" t="n"/>
-      <c r="S50" s="471" t="n"/>
-      <c r="T50" s="471" t="n"/>
-      <c r="U50" s="471" t="n"/>
-      <c r="V50" s="471" t="n"/>
-      <c r="W50" s="471" t="n"/>
-      <c r="X50" s="471" t="n"/>
-      <c r="Y50" s="471" t="n"/>
-      <c r="Z50" s="471" t="n"/>
-      <c r="AA50" s="471" t="n"/>
-      <c r="AB50" s="471" t="n"/>
-      <c r="AC50" s="471" t="n"/>
-      <c r="AD50" s="471" t="n"/>
-      <c r="AE50" s="471" t="n"/>
-      <c r="AF50" s="471" t="n"/>
-      <c r="AG50" s="471" t="n"/>
-      <c r="AH50" s="471" t="n"/>
-      <c r="AI50" s="471" t="n"/>
-      <c r="AJ50" s="471" t="n"/>
-      <c r="AK50" s="471" t="n"/>
-      <c r="AL50" s="471" t="n"/>
-      <c r="AM50" s="471" t="n"/>
-      <c r="AN50" s="472" t="n"/>
+    <row r="47" ht="24" customHeight="1" s="264">
+      <c r="A47" s="522" t="inlineStr">
+        <is>
+          <t>NOTICE — Rework may only proceed against an approved method. Repair (a permanent departure from the drawing) additionally requires a Concession Permit (FRM-656). Ref: SOP-505 / FRM-651. Retain: 10 years. Enter data only in white input cells. Do not add, delete or resize columns/rows.</t>
+        </is>
+      </c>
+      <c r="B47" s="471" t="n"/>
+      <c r="C47" s="471" t="n"/>
+      <c r="D47" s="471" t="n"/>
+      <c r="E47" s="471" t="n"/>
+      <c r="F47" s="471" t="n"/>
+      <c r="G47" s="471" t="n"/>
+      <c r="H47" s="471" t="n"/>
+      <c r="I47" s="471" t="n"/>
+      <c r="J47" s="471" t="n"/>
+      <c r="K47" s="471" t="n"/>
+      <c r="L47" s="471" t="n"/>
+      <c r="M47" s="471" t="n"/>
+      <c r="N47" s="471" t="n"/>
+      <c r="O47" s="471" t="n"/>
+      <c r="P47" s="471" t="n"/>
+      <c r="Q47" s="471" t="n"/>
+      <c r="R47" s="471" t="n"/>
+      <c r="S47" s="471" t="n"/>
+      <c r="T47" s="471" t="n"/>
+      <c r="U47" s="471" t="n"/>
+      <c r="V47" s="471" t="n"/>
+      <c r="W47" s="471" t="n"/>
+      <c r="X47" s="471" t="n"/>
+      <c r="Y47" s="471" t="n"/>
+      <c r="Z47" s="471" t="n"/>
+      <c r="AA47" s="471" t="n"/>
+      <c r="AB47" s="471" t="n"/>
+      <c r="AC47" s="471" t="n"/>
+      <c r="AD47" s="471" t="n"/>
+      <c r="AE47" s="471" t="n"/>
+      <c r="AF47" s="471" t="n"/>
+      <c r="AG47" s="471" t="n"/>
+      <c r="AH47" s="471" t="n"/>
+      <c r="AI47" s="471" t="n"/>
+      <c r="AJ47" s="471" t="n"/>
+      <c r="AK47" s="471" t="n"/>
+      <c r="AL47" s="471" t="n"/>
+      <c r="AM47" s="471" t="n"/>
+      <c r="AN47" s="472" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="134">
-    <mergeCell ref="V36:AE36"/>
-    <mergeCell ref="U42:AA42"/>
+  <mergeCells count="123">
     <mergeCell ref="A21:AN21"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="AE6:AH6"/>
     <mergeCell ref="A14:AN14"/>
-    <mergeCell ref="F37:U37"/>
-    <mergeCell ref="H42:T42"/>
-    <mergeCell ref="V37:AE37"/>
     <mergeCell ref="A9:G9"/>
     <mergeCell ref="AE4:AH4"/>
-    <mergeCell ref="AF36:AI36"/>
-    <mergeCell ref="AB42:AN42"/>
+    <mergeCell ref="A39:G39"/>
     <mergeCell ref="U9:AA9"/>
-    <mergeCell ref="A43:AN43"/>
     <mergeCell ref="AF34:AI34"/>
+    <mergeCell ref="A27:B27"/>
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A40:AN40"/>
     <mergeCell ref="F34:U34"/>
@@ -7816,7 +7663,6 @@
     <mergeCell ref="I2:AD4"/>
     <mergeCell ref="F30:U30"/>
     <mergeCell ref="C34:E34"/>
-    <mergeCell ref="AJ36:AN36"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="F33:U33"/>
     <mergeCell ref="A2:H6"/>
@@ -7824,108 +7670,104 @@
     <mergeCell ref="U13:AA13"/>
     <mergeCell ref="AJ29:AN29"/>
     <mergeCell ref="A25:AN25"/>
-    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="AB39:AN39"/>
     <mergeCell ref="A18:AN18"/>
+    <mergeCell ref="A42:M42"/>
     <mergeCell ref="AJ31:AN31"/>
+    <mergeCell ref="V27:AE27"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="F31:U31"/>
-    <mergeCell ref="A50:AN50"/>
+    <mergeCell ref="F28:U28"/>
     <mergeCell ref="AF32:AI32"/>
     <mergeCell ref="H13:T13"/>
+    <mergeCell ref="AB38:AN38"/>
     <mergeCell ref="I5:AD5"/>
     <mergeCell ref="AF35:AI35"/>
-    <mergeCell ref="AF38:AI38"/>
+    <mergeCell ref="A47:AN47"/>
     <mergeCell ref="A10:G10"/>
     <mergeCell ref="AE5:AH5"/>
     <mergeCell ref="U10:AA10"/>
     <mergeCell ref="AB10:AN10"/>
     <mergeCell ref="A20:AN20"/>
-    <mergeCell ref="AJ38:AN38"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="AF37:AI37"/>
-    <mergeCell ref="H26:T26"/>
-    <mergeCell ref="A44:AN44"/>
+    <mergeCell ref="AF27:AI27"/>
     <mergeCell ref="AI3:AN3"/>
     <mergeCell ref="C32:E32"/>
     <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="AA45:AN45"/>
     <mergeCell ref="H10:T10"/>
-    <mergeCell ref="H41:T41"/>
     <mergeCell ref="A15:AN15"/>
     <mergeCell ref="AI5:AN5"/>
     <mergeCell ref="AJ33:AN33"/>
     <mergeCell ref="V29:AE29"/>
+    <mergeCell ref="H39:T39"/>
     <mergeCell ref="C33:E33"/>
     <mergeCell ref="AJ35:AN35"/>
     <mergeCell ref="V31:AE31"/>
-    <mergeCell ref="F36:U36"/>
     <mergeCell ref="A7:AN7"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="A41:AN41"/>
     <mergeCell ref="U12:AA12"/>
     <mergeCell ref="AB12:AN12"/>
-    <mergeCell ref="AA46:AN48"/>
     <mergeCell ref="C35:E35"/>
     <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A27:AN27"/>
     <mergeCell ref="V32:AE32"/>
     <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A38:G38"/>
     <mergeCell ref="H12:T12"/>
     <mergeCell ref="AB13:AN13"/>
     <mergeCell ref="A17:AN17"/>
+    <mergeCell ref="AF28:AI28"/>
     <mergeCell ref="A22:AN22"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="U26:AA26"/>
+    <mergeCell ref="AA43:AN45"/>
     <mergeCell ref="A19:AN19"/>
-    <mergeCell ref="A28:AN28"/>
+    <mergeCell ref="H38:T38"/>
     <mergeCell ref="V33:AE33"/>
     <mergeCell ref="I6:AD6"/>
-    <mergeCell ref="A39:AN39"/>
+    <mergeCell ref="C28:E28"/>
     <mergeCell ref="AI2:AN2"/>
-    <mergeCell ref="A45:M45"/>
-    <mergeCell ref="C37:E37"/>
     <mergeCell ref="V35:AE35"/>
-    <mergeCell ref="AB26:AN26"/>
     <mergeCell ref="AE3:AH3"/>
-    <mergeCell ref="AJ37:AN37"/>
     <mergeCell ref="A32:B32"/>
-    <mergeCell ref="AB41:AN41"/>
     <mergeCell ref="C30:E30"/>
     <mergeCell ref="U11:AA11"/>
     <mergeCell ref="V34:AE34"/>
-    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="V28:AE28"/>
+    <mergeCell ref="N42:Z42"/>
     <mergeCell ref="F32:U32"/>
     <mergeCell ref="AB9:AN9"/>
+    <mergeCell ref="N43:Z45"/>
     <mergeCell ref="V30:AE30"/>
     <mergeCell ref="F35:U35"/>
+    <mergeCell ref="A37:AN37"/>
+    <mergeCell ref="A46:AN46"/>
     <mergeCell ref="H11:T11"/>
-    <mergeCell ref="F38:U38"/>
-    <mergeCell ref="A46:M48"/>
     <mergeCell ref="AB11:AN11"/>
     <mergeCell ref="AI6:AN6"/>
+    <mergeCell ref="A26:AN26"/>
+    <mergeCell ref="F27:U27"/>
+    <mergeCell ref="U39:AA39"/>
+    <mergeCell ref="AJ27:AN27"/>
     <mergeCell ref="AI4:AN4"/>
     <mergeCell ref="A23:AN23"/>
+    <mergeCell ref="U38:AA38"/>
     <mergeCell ref="A8:AN8"/>
     <mergeCell ref="A13:G13"/>
-    <mergeCell ref="N45:Z45"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="AA42:AN42"/>
+    <mergeCell ref="A43:M45"/>
+    <mergeCell ref="AJ28:AN28"/>
     <mergeCell ref="F29:U29"/>
-    <mergeCell ref="V38:AE38"/>
     <mergeCell ref="AJ30:AN30"/>
     <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="A49:AN49"/>
     <mergeCell ref="AE2:AH2"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="U41:AA41"/>
-    <mergeCell ref="N46:Z48"/>
+    <mergeCell ref="A36:AN36"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="C29:E29"/>
     <mergeCell ref="AJ32:AN32"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A42:G42"/>
   </mergeCells>
-  <conditionalFormatting sqref="AF30:AF38">
+  <conditionalFormatting sqref="AF28:AF35">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"PASS"</formula>
     </cfRule>
@@ -7937,13 +7779,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="AF30 AF31 AF32 AF33 AF34 AF35 AF36 AF37 AF38" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="AF28 AF29 AF30 AF31 AF32 AF33 AF34 AF35" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=LISTS!$A$2:$A$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
